--- a/research/traditional_assets/database/data/singapore/singapore_semiconductor.xlsx
+++ b/research/traditional_assets/database/data/singapore/singapore_semiconductor.xlsx
@@ -1403,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1540,22 +1540,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1174892188913704</v>
+        <v>0.1173268372192551</v>
       </c>
       <c r="C2">
-        <v>29.28821653143249</v>
+        <v>29.04736212469902</v>
       </c>
       <c r="D2">
-        <v>23.34821653143249</v>
+        <v>23.40122212469902</v>
       </c>
       <c r="E2">
-        <v>-0.586</v>
+        <v>-0.29214</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.29386</v>
       </c>
       <c r="G2">
         <v>5.94</v>
@@ -1576,28 +1576,28 @@
         <v>1.4</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.014781158</v>
       </c>
       <c r="N2">
-        <v>1.4</v>
+        <v>1.385218842</v>
       </c>
       <c r="O2">
-        <v>0.238</v>
+        <v>0.23548720314</v>
       </c>
       <c r="P2">
-        <v>1.162</v>
+        <v>1.14973163886</v>
       </c>
       <c r="Q2">
-        <v>1.922</v>
+        <v>1.90973163886</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1174892188913704</v>
+        <v>0.1180902497164193</v>
       </c>
       <c r="T2">
-        <v>1.655640159154051</v>
+        <v>1.669520778670192</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1614,7 +1614,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>94.71517725471848</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1622,22 +1622,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1173268372192551</v>
+        <v>0.1171644555471398</v>
       </c>
       <c r="C3">
-        <v>29.04736212469902</v>
+        <v>28.80674893431899</v>
       </c>
       <c r="D3">
-        <v>23.40122212469902</v>
+        <v>23.45446893431899</v>
       </c>
       <c r="E3">
-        <v>-0.29214</v>
+        <v>0.001720000000000055</v>
       </c>
       <c r="F3">
-        <v>0.29386</v>
+        <v>0.58772</v>
       </c>
       <c r="G3">
         <v>5.94</v>
@@ -1658,28 +1658,28 @@
         <v>1.4</v>
       </c>
       <c r="M3">
-        <v>0.014781158</v>
+        <v>0.029562316</v>
       </c>
       <c r="N3">
-        <v>1.385218842</v>
+        <v>1.370437684</v>
       </c>
       <c r="O3">
-        <v>0.23548720314</v>
+        <v>0.23297440628</v>
       </c>
       <c r="P3">
-        <v>1.14973163886</v>
+        <v>1.13746327772</v>
       </c>
       <c r="Q3">
-        <v>1.90973163886</v>
+        <v>1.89746327772</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1180902497164193</v>
+        <v>0.1187035464766732</v>
       </c>
       <c r="T3">
-        <v>1.669520778670192</v>
+        <v>1.683684676135641</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1696,7 +1696,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>94.71517725471848</v>
+        <v>47.35758862735923</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1704,22 +1704,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1171644555471398</v>
+        <v>0.1170020738750244</v>
       </c>
       <c r="C4">
-        <v>28.80674893431899</v>
+        <v>28.56637861062837</v>
       </c>
       <c r="D4">
-        <v>23.45446893431899</v>
+        <v>23.50795861062837</v>
       </c>
       <c r="E4">
-        <v>0.001720000000000055</v>
+        <v>0.29558</v>
       </c>
       <c r="F4">
-        <v>0.58772</v>
+        <v>0.8815799999999999</v>
       </c>
       <c r="G4">
         <v>5.94</v>
@@ -1740,28 +1740,28 @@
         <v>1.4</v>
       </c>
       <c r="M4">
-        <v>0.029562316</v>
+        <v>0.04434347399999999</v>
       </c>
       <c r="N4">
-        <v>1.370437684</v>
+        <v>1.355656526</v>
       </c>
       <c r="O4">
-        <v>0.23297440628</v>
+        <v>0.23046160942</v>
       </c>
       <c r="P4">
-        <v>1.13746327772</v>
+        <v>1.12519491658</v>
       </c>
       <c r="Q4">
-        <v>1.89746327772</v>
+        <v>1.88519491658</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1187035464766732</v>
+        <v>0.119329488530953</v>
       </c>
       <c r="T4">
-        <v>1.683684676135641</v>
+        <v>1.698140612724089</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1778,7 +1778,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>47.35758862735923</v>
+        <v>31.57172575157283</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1786,22 +1786,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1170020738750244</v>
+        <v>0.1168396922029091</v>
       </c>
       <c r="C5">
-        <v>28.56637861062837</v>
+        <v>28.32625281905242</v>
       </c>
       <c r="D5">
-        <v>23.50795861062837</v>
+        <v>23.56169281905242</v>
       </c>
       <c r="E5">
-        <v>0.29558</v>
+        <v>0.5894400000000001</v>
       </c>
       <c r="F5">
-        <v>0.8815799999999999</v>
+        <v>1.17544</v>
       </c>
       <c r="G5">
         <v>5.94</v>
@@ -1822,28 +1822,28 @@
         <v>1.4</v>
       </c>
       <c r="M5">
-        <v>0.04434347399999999</v>
+        <v>0.059124632</v>
       </c>
       <c r="N5">
-        <v>1.355656526</v>
+        <v>1.340875368</v>
       </c>
       <c r="O5">
-        <v>0.23046160942</v>
+        <v>0.22794881256</v>
       </c>
       <c r="P5">
-        <v>1.12519491658</v>
+        <v>1.11292655544</v>
       </c>
       <c r="Q5">
-        <v>1.88519491658</v>
+        <v>1.87292655544</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.119329488530953</v>
+        <v>0.119968471044697</v>
       </c>
       <c r="T5">
-        <v>1.698140612724089</v>
+        <v>1.712897714658129</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1860,7 +1860,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>31.57172575157283</v>
+        <v>23.67879431367962</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1868,22 +1868,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1168396922029091</v>
+        <v>0.1166773105307938</v>
       </c>
       <c r="C6">
-        <v>28.32625281905242</v>
+        <v>28.08637324027853</v>
       </c>
       <c r="D6">
-        <v>23.56169281905242</v>
+        <v>23.61567324027853</v>
       </c>
       <c r="E6">
-        <v>0.5894400000000001</v>
+        <v>0.8833000000000001</v>
       </c>
       <c r="F6">
-        <v>1.17544</v>
+        <v>1.4693</v>
       </c>
       <c r="G6">
         <v>5.94</v>
@@ -1904,28 +1904,28 @@
         <v>1.4</v>
       </c>
       <c r="M6">
-        <v>0.059124632</v>
+        <v>0.07390579</v>
       </c>
       <c r="N6">
-        <v>1.340875368</v>
+        <v>1.32609421</v>
       </c>
       <c r="O6">
-        <v>0.22794881256</v>
+        <v>0.2254360157</v>
       </c>
       <c r="P6">
-        <v>1.11292655544</v>
+        <v>1.1006581943</v>
       </c>
       <c r="Q6">
-        <v>1.87292655544</v>
+        <v>1.8606581943</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.119968471044697</v>
+        <v>0.1206209058218882</v>
       </c>
       <c r="T6">
-        <v>1.712897714658129</v>
+        <v>1.72796549242236</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>23.67879431367962</v>
+        <v>18.94303545094369</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1950,22 +1950,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1166773105307938</v>
+        <v>0.1165149288586784</v>
       </c>
       <c r="C7">
-        <v>28.08637324027853</v>
+        <v>27.8467415704314</v>
       </c>
       <c r="D7">
-        <v>23.61567324027853</v>
+        <v>23.6699015704314</v>
       </c>
       <c r="E7">
-        <v>0.8833000000000001</v>
+        <v>1.17716</v>
       </c>
       <c r="F7">
-        <v>1.4693</v>
+        <v>1.76316</v>
       </c>
       <c r="G7">
         <v>5.94</v>
@@ -1986,28 +1986,28 @@
         <v>1.4</v>
       </c>
       <c r="M7">
-        <v>0.07390579</v>
+        <v>0.088686948</v>
       </c>
       <c r="N7">
-        <v>1.32609421</v>
+        <v>1.311313052</v>
       </c>
       <c r="O7">
-        <v>0.2254360157</v>
+        <v>0.22292321884</v>
       </c>
       <c r="P7">
-        <v>1.1006581943</v>
+        <v>1.08838983316</v>
       </c>
       <c r="Q7">
-        <v>1.8606581943</v>
+        <v>1.84838983316</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1206209058218882</v>
+        <v>0.1212872221900834</v>
       </c>
       <c r="T7">
-        <v>1.72796549242236</v>
+        <v>1.743353861202851</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2024,7 +2024,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>18.94303545094369</v>
+        <v>15.78586287578641</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2032,22 +2032,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1165149288586784</v>
+        <v>0.1163525471865631</v>
       </c>
       <c r="C8">
-        <v>27.8467415704314</v>
+        <v>27.60735952125079</v>
       </c>
       <c r="D8">
-        <v>23.6699015704314</v>
+        <v>23.72437952125079</v>
       </c>
       <c r="E8">
-        <v>1.17716</v>
+        <v>1.47102</v>
       </c>
       <c r="F8">
-        <v>1.76316</v>
+        <v>2.05702</v>
       </c>
       <c r="G8">
         <v>5.94</v>
@@ -2068,28 +2068,28 @@
         <v>1.4</v>
       </c>
       <c r="M8">
-        <v>0.08868694799999999</v>
+        <v>0.103468106</v>
       </c>
       <c r="N8">
-        <v>1.311313052</v>
+        <v>1.296531894</v>
       </c>
       <c r="O8">
-        <v>0.22292321884</v>
+        <v>0.22041042198</v>
       </c>
       <c r="P8">
-        <v>1.08838983316</v>
+        <v>1.07612147202</v>
       </c>
       <c r="Q8">
-        <v>1.84838983316</v>
+        <v>1.83612147202</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1212872221900834</v>
+        <v>0.121967867942541</v>
       </c>
       <c r="T8">
-        <v>1.743353861202851</v>
+        <v>1.759073162645288</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2106,7 +2106,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>15.78586287578641</v>
+        <v>13.53073960781693</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2114,22 +2114,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1163525471865631</v>
+        <v>0.1162897655144478</v>
       </c>
       <c r="C9">
-        <v>27.60735952125079</v>
+        <v>27.3346296272367</v>
       </c>
       <c r="D9">
-        <v>23.72437952125079</v>
+        <v>23.7455096272367</v>
       </c>
       <c r="E9">
-        <v>1.47102</v>
+        <v>1.76488</v>
       </c>
       <c r="F9">
-        <v>2.05702</v>
+        <v>2.35088</v>
       </c>
       <c r="G9">
         <v>5.94</v>
@@ -2150,45 +2150,45 @@
         <v>1.4</v>
       </c>
       <c r="M9">
-        <v>0.103468106</v>
+        <v>0.121775584</v>
       </c>
       <c r="N9">
-        <v>1.296531894</v>
+        <v>1.278224416</v>
       </c>
       <c r="O9">
-        <v>0.22041042198</v>
+        <v>0.21729815072</v>
       </c>
       <c r="P9">
-        <v>1.07612147202</v>
+        <v>1.06092626528</v>
       </c>
       <c r="Q9">
-        <v>1.83612147202</v>
+        <v>1.82092626528</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.121967867942541</v>
+        <v>0.1226633103417911</v>
       </c>
       <c r="T9">
-        <v>1.759073162645288</v>
+        <v>1.775134188032126</v>
       </c>
       <c r="U9">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V9">
         <v>0.17</v>
       </c>
       <c r="W9">
-        <v>0.04174899999999999</v>
+        <v>0.042994</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y9">
-        <v>13.53073960781692</v>
+        <v>11.49655747083093</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2196,22 +2196,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1162897655144478</v>
+        <v>0.1161398338423325</v>
       </c>
       <c r="C10">
-        <v>27.3346296272367</v>
+        <v>27.09138396294331</v>
       </c>
       <c r="D10">
-        <v>23.7455096272367</v>
+        <v>23.79612396294331</v>
       </c>
       <c r="E10">
-        <v>1.76488</v>
+        <v>2.05874</v>
       </c>
       <c r="F10">
-        <v>2.35088</v>
+        <v>2.64474</v>
       </c>
       <c r="G10">
         <v>5.94</v>
@@ -2232,28 +2232,28 @@
         <v>1.4</v>
       </c>
       <c r="M10">
-        <v>0.121775584</v>
+        <v>0.136997532</v>
       </c>
       <c r="N10">
-        <v>1.278224416</v>
+        <v>1.263002468</v>
       </c>
       <c r="O10">
-        <v>0.21729815072</v>
+        <v>0.21471041956</v>
       </c>
       <c r="P10">
-        <v>1.06092626528</v>
+        <v>1.04829204844</v>
       </c>
       <c r="Q10">
-        <v>1.82092626528</v>
+        <v>1.80829204844</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1226633103417911</v>
+        <v>0.1233740371893763</v>
       </c>
       <c r="T10">
-        <v>1.775134188032126</v>
+        <v>1.791548202987906</v>
       </c>
       <c r="U10">
         <v>0.0518</v>
@@ -2270,7 +2270,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>11.49655747083093</v>
+        <v>10.21916219629416</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2278,22 +2278,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1161398338423325</v>
+        <v>0.1161310021702171</v>
       </c>
       <c r="C11">
-        <v>27.09138396294331</v>
+        <v>26.8005121126635</v>
       </c>
       <c r="D11">
-        <v>23.79612396294331</v>
+        <v>23.7991121126635</v>
       </c>
       <c r="E11">
-        <v>2.05874</v>
+        <v>2.3526</v>
       </c>
       <c r="F11">
-        <v>2.64474</v>
+        <v>2.9386</v>
       </c>
       <c r="G11">
         <v>5.94</v>
@@ -2314,45 +2314,45 @@
         <v>1.4</v>
       </c>
       <c r="M11">
-        <v>0.136997532</v>
+        <v>0.1572151</v>
       </c>
       <c r="N11">
-        <v>1.263002468</v>
+        <v>1.2427849</v>
       </c>
       <c r="O11">
-        <v>0.21471041956</v>
+        <v>0.211273433</v>
       </c>
       <c r="P11">
-        <v>1.04829204844</v>
+        <v>1.031511467</v>
       </c>
       <c r="Q11">
-        <v>1.80829204844</v>
+        <v>1.791511467</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1233740371893763</v>
+        <v>0.1241005579669079</v>
       </c>
       <c r="T11">
-        <v>1.791548202987906</v>
+        <v>1.808326973831592</v>
       </c>
       <c r="U11">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V11">
         <v>0.17</v>
       </c>
       <c r="W11">
-        <v>0.042994</v>
+        <v>0.044405</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y11">
-        <v>10.21916219629416</v>
+        <v>8.904997039088485</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2360,22 +2360,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1161310021702171</v>
+        <v>0.1159951804981018</v>
       </c>
       <c r="C12">
-        <v>26.8005121126635</v>
+        <v>26.55270135962128</v>
       </c>
       <c r="D12">
-        <v>23.7991121126635</v>
+        <v>23.84516135962128</v>
       </c>
       <c r="E12">
-        <v>2.3526</v>
+        <v>2.64646</v>
       </c>
       <c r="F12">
-        <v>2.9386</v>
+        <v>3.23246</v>
       </c>
       <c r="G12">
         <v>5.94</v>
@@ -2396,28 +2396,28 @@
         <v>1.4</v>
       </c>
       <c r="M12">
-        <v>0.1572151</v>
+        <v>0.17293661</v>
       </c>
       <c r="N12">
-        <v>1.2427849</v>
+        <v>1.22706339</v>
       </c>
       <c r="O12">
-        <v>0.211273433</v>
+        <v>0.2086007763</v>
       </c>
       <c r="P12">
-        <v>1.031511467</v>
+        <v>1.0184626137</v>
       </c>
       <c r="Q12">
-        <v>1.791511467</v>
+        <v>1.7784626137</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1241005579669079</v>
+        <v>0.124843405054047</v>
       </c>
       <c r="T12">
-        <v>1.808326973831592</v>
+        <v>1.825482795705473</v>
       </c>
       <c r="U12">
         <v>0.0535</v>
@@ -2434,7 +2434,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>8.904997039088485</v>
+        <v>8.095451853716803</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2442,22 +2442,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1159951804981018</v>
+        <v>0.1159390388259865</v>
       </c>
       <c r="C13">
-        <v>26.55270135962128</v>
+        <v>26.27792783775095</v>
       </c>
       <c r="D13">
-        <v>23.84516135962128</v>
+        <v>23.86424783775095</v>
       </c>
       <c r="E13">
-        <v>2.64646</v>
+        <v>2.94032</v>
       </c>
       <c r="F13">
-        <v>3.23246</v>
+        <v>3.52632</v>
       </c>
       <c r="G13">
         <v>5.94</v>
@@ -2478,45 +2478,45 @@
         <v>1.4</v>
       </c>
       <c r="M13">
-        <v>0.17293661</v>
+        <v>0.191479176</v>
       </c>
       <c r="N13">
-        <v>1.22706339</v>
+        <v>1.208520824</v>
       </c>
       <c r="O13">
-        <v>0.2086007763</v>
+        <v>0.20544854008</v>
       </c>
       <c r="P13">
-        <v>1.0184626137</v>
+        <v>1.00307228392</v>
       </c>
       <c r="Q13">
-        <v>1.7784626137</v>
+        <v>1.76307228392</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.124843405054047</v>
+        <v>0.1256031350295301</v>
       </c>
       <c r="T13">
-        <v>1.825482795705473</v>
+        <v>1.843028522621942</v>
       </c>
       <c r="U13">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V13">
         <v>0.17</v>
       </c>
       <c r="W13">
-        <v>0.044405</v>
+        <v>0.045069</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y13">
-        <v>8.095451853716803</v>
+        <v>7.31150002442041</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2524,22 +2524,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1159390388259865</v>
+        <v>0.1158098571538711</v>
       </c>
       <c r="C14">
-        <v>26.27792783775095</v>
+        <v>26.02810197186838</v>
       </c>
       <c r="D14">
-        <v>23.86424783775095</v>
+        <v>23.90828197186838</v>
       </c>
       <c r="E14">
-        <v>2.94032</v>
+        <v>3.23418</v>
       </c>
       <c r="F14">
-        <v>3.52632</v>
+        <v>3.82018</v>
       </c>
       <c r="G14">
         <v>5.94</v>
@@ -2560,28 +2560,28 @@
         <v>1.4</v>
       </c>
       <c r="M14">
-        <v>0.191479176</v>
+        <v>0.207435774</v>
       </c>
       <c r="N14">
-        <v>1.208520824</v>
+        <v>1.192564226</v>
       </c>
       <c r="O14">
-        <v>0.20544854008</v>
+        <v>0.20273591842</v>
       </c>
       <c r="P14">
-        <v>1.00307228392</v>
+        <v>0.98982830758</v>
       </c>
       <c r="Q14">
-        <v>1.76307228392</v>
+        <v>1.74982830758</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1256031350295301</v>
+        <v>0.1263803300619208</v>
       </c>
       <c r="T14">
-        <v>1.843028522621942</v>
+        <v>1.860977599582468</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2598,7 +2598,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>7.31150002442041</v>
+        <v>6.74907694561884</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2606,22 +2606,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1158098571538711</v>
+        <v>0.1156806754817558</v>
       </c>
       <c r="C15">
-        <v>26.02810197186838</v>
+        <v>25.77843890930836</v>
       </c>
       <c r="D15">
-        <v>23.90828197186838</v>
+        <v>23.95247890930835</v>
       </c>
       <c r="E15">
-        <v>3.23418</v>
+        <v>3.52804</v>
       </c>
       <c r="F15">
-        <v>3.82018</v>
+        <v>4.11404</v>
       </c>
       <c r="G15">
         <v>5.94</v>
@@ -2642,28 +2642,28 @@
         <v>1.4</v>
       </c>
       <c r="M15">
-        <v>0.207435774</v>
+        <v>0.223392372</v>
       </c>
       <c r="N15">
-        <v>1.192564226</v>
+        <v>1.176607628</v>
       </c>
       <c r="O15">
-        <v>0.20273591842</v>
+        <v>0.20002329676</v>
       </c>
       <c r="P15">
-        <v>0.98982830758</v>
+        <v>0.97658433124</v>
       </c>
       <c r="Q15">
-        <v>1.74982830758</v>
+        <v>1.73658433124</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1263803300619208</v>
+        <v>0.1271755993973905</v>
       </c>
       <c r="T15">
-        <v>1.860977599582468</v>
+        <v>1.879344096937425</v>
       </c>
       <c r="U15">
         <v>0.0543</v>
@@ -2680,7 +2680,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>6.74907694561884</v>
+        <v>6.267000020931779</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2688,22 +2688,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1156806754817558</v>
+        <v>0.1156759938096405</v>
       </c>
       <c r="C16">
-        <v>25.77843890930836</v>
+        <v>25.48618371872128</v>
       </c>
       <c r="D16">
-        <v>23.95247890930835</v>
+        <v>23.95408371872128</v>
       </c>
       <c r="E16">
-        <v>3.52804</v>
+        <v>3.821900000000001</v>
       </c>
       <c r="F16">
-        <v>4.11404</v>
+        <v>4.407900000000001</v>
       </c>
       <c r="G16">
         <v>5.94</v>
@@ -2724,45 +2724,45 @@
         <v>1.4</v>
       </c>
       <c r="M16">
-        <v>0.223392372</v>
+        <v>0.24375687</v>
       </c>
       <c r="N16">
-        <v>1.176607628</v>
+        <v>1.15624313</v>
       </c>
       <c r="O16">
-        <v>0.20002329676</v>
+        <v>0.1965613321</v>
       </c>
       <c r="P16">
-        <v>0.97658433124</v>
+        <v>0.9596817978999999</v>
       </c>
       <c r="Q16">
-        <v>1.73658433124</v>
+        <v>1.7196817979</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1271755993973905</v>
+        <v>0.1279895809525182</v>
       </c>
       <c r="T16">
-        <v>1.879344096937425</v>
+        <v>1.898142747171321</v>
       </c>
       <c r="U16">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V16">
         <v>0.17</v>
       </c>
       <c r="W16">
-        <v>0.045069</v>
+        <v>0.045899</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y16">
-        <v>6.267000020931779</v>
+        <v>5.743427867284313</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2770,22 +2770,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1156759938096405</v>
+        <v>0.1155551121375251</v>
       </c>
       <c r="C17">
-        <v>25.48618371872129</v>
+        <v>25.23383479375476</v>
       </c>
       <c r="D17">
-        <v>23.95408371872128</v>
+        <v>23.99559479375476</v>
       </c>
       <c r="E17">
-        <v>3.8219</v>
+        <v>4.11576</v>
       </c>
       <c r="F17">
-        <v>4.4079</v>
+        <v>4.70176</v>
       </c>
       <c r="G17">
         <v>5.94</v>
@@ -2806,28 +2806,28 @@
         <v>1.4</v>
       </c>
       <c r="M17">
-        <v>0.24375687</v>
+        <v>0.260007328</v>
       </c>
       <c r="N17">
-        <v>1.15624313</v>
+        <v>1.139992672</v>
       </c>
       <c r="O17">
-        <v>0.1965613321</v>
+        <v>0.19379875424</v>
       </c>
       <c r="P17">
-        <v>0.9596817979</v>
+        <v>0.9461939177599999</v>
       </c>
       <c r="Q17">
-        <v>1.7196817979</v>
+        <v>1.70619391776</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1279895809525182</v>
+        <v>0.1288229430208633</v>
       </c>
       <c r="T17">
-        <v>1.898142747171321</v>
+        <v>1.917388984315549</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2844,7 +2844,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.743427867284315</v>
+        <v>5.384463625579045</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2852,22 +2852,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1155551121375251</v>
+        <v>0.1154342304654098</v>
       </c>
       <c r="C18">
-        <v>25.23383479375476</v>
+        <v>24.98162999124433</v>
       </c>
       <c r="D18">
-        <v>23.99559479375476</v>
+        <v>24.03724999124433</v>
       </c>
       <c r="E18">
-        <v>4.11576</v>
+        <v>4.40962</v>
       </c>
       <c r="F18">
-        <v>4.70176</v>
+        <v>4.995620000000001</v>
       </c>
       <c r="G18">
         <v>5.94</v>
@@ -2888,28 +2888,28 @@
         <v>1.4</v>
       </c>
       <c r="M18">
-        <v>0.260007328</v>
+        <v>0.2762577860000001</v>
       </c>
       <c r="N18">
-        <v>1.139992672</v>
+        <v>1.123742214</v>
       </c>
       <c r="O18">
-        <v>0.19379875424</v>
+        <v>0.19103617638</v>
       </c>
       <c r="P18">
-        <v>0.9461939177599999</v>
+        <v>0.9327060376199999</v>
       </c>
       <c r="Q18">
-        <v>1.70619391776</v>
+        <v>1.69270603762</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1288229430208633</v>
+        <v>0.1296763861029034</v>
       </c>
       <c r="T18">
-        <v>1.917388984315549</v>
+        <v>1.93709898621024</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2926,7 +2926,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>5.384463625579045</v>
+        <v>5.067730471133218</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2934,22 +2934,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1154342304654098</v>
+        <v>0.1153133487932945</v>
       </c>
       <c r="C19">
-        <v>24.98162999124433</v>
+        <v>24.72957006306415</v>
       </c>
       <c r="D19">
-        <v>24.03724999124433</v>
+        <v>24.07905006306415</v>
       </c>
       <c r="E19">
-        <v>4.40962</v>
+        <v>4.70348</v>
       </c>
       <c r="F19">
-        <v>4.995620000000001</v>
+        <v>5.28948</v>
       </c>
       <c r="G19">
         <v>5.94</v>
@@ -2970,28 +2970,28 @@
         <v>1.4</v>
       </c>
       <c r="M19">
-        <v>0.2762577860000001</v>
+        <v>0.292508244</v>
       </c>
       <c r="N19">
-        <v>1.123742214</v>
+        <v>1.107491756</v>
       </c>
       <c r="O19">
-        <v>0.19103617638</v>
+        <v>0.18827359852</v>
       </c>
       <c r="P19">
-        <v>0.9327060376199999</v>
+        <v>0.9192181574799999</v>
       </c>
       <c r="Q19">
-        <v>1.69270603762</v>
+        <v>1.67921815748</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1296763861029034</v>
+        <v>0.1305506448698713</v>
       </c>
       <c r="T19">
-        <v>1.93709898621024</v>
+        <v>1.95728971985846</v>
       </c>
       <c r="U19">
         <v>0.0553</v>
@@ -3008,7 +3008,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>5.067730471133218</v>
+        <v>4.786189889403595</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3016,22 +3016,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1153133487932945</v>
+        <v>0.1151924671211792</v>
       </c>
       <c r="C20">
-        <v>24.72957006306415</v>
+        <v>24.47765576632743</v>
       </c>
       <c r="D20">
-        <v>24.07905006306415</v>
+        <v>24.12099576632743</v>
       </c>
       <c r="E20">
-        <v>4.703479999999999</v>
+        <v>4.997339999999999</v>
       </c>
       <c r="F20">
-        <v>5.289479999999999</v>
+        <v>5.58334</v>
       </c>
       <c r="G20">
         <v>5.94</v>
@@ -3052,28 +3052,28 @@
         <v>1.4</v>
       </c>
       <c r="M20">
-        <v>0.292508244</v>
+        <v>0.308758702</v>
       </c>
       <c r="N20">
-        <v>1.107491756</v>
+        <v>1.091241298</v>
       </c>
       <c r="O20">
-        <v>0.18827359852</v>
+        <v>0.18551102066</v>
       </c>
       <c r="P20">
-        <v>0.9192181574799999</v>
+        <v>0.9057302773399999</v>
       </c>
       <c r="Q20">
-        <v>1.67921815748</v>
+        <v>1.66573027734</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1305506448698713</v>
+        <v>0.1314464902730607</v>
       </c>
       <c r="T20">
-        <v>1.95728971985846</v>
+        <v>1.97797899013997</v>
       </c>
       <c r="U20">
         <v>0.0553</v>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>4.786189889403596</v>
+        <v>4.534285158382353</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3098,22 +3098,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1151924671211792</v>
+        <v>0.1154865854490638</v>
       </c>
       <c r="C21">
-        <v>24.47765576632743</v>
+        <v>24.08199099434744</v>
       </c>
       <c r="D21">
-        <v>24.12099576632743</v>
+        <v>24.01919099434744</v>
       </c>
       <c r="E21">
-        <v>4.997339999999999</v>
+        <v>5.2912</v>
       </c>
       <c r="F21">
-        <v>5.58334</v>
+        <v>5.8772</v>
       </c>
       <c r="G21">
         <v>5.94</v>
@@ -3134,45 +3134,45 @@
         <v>1.4</v>
       </c>
       <c r="M21">
-        <v>0.308758702</v>
+        <v>0.33970216</v>
       </c>
       <c r="N21">
-        <v>1.091241298</v>
+        <v>1.06029784</v>
       </c>
       <c r="O21">
-        <v>0.18551102066</v>
+        <v>0.1802506328</v>
       </c>
       <c r="P21">
-        <v>0.9057302773399999</v>
+        <v>0.8800472071999998</v>
       </c>
       <c r="Q21">
-        <v>1.66573027734</v>
+        <v>1.6400472072</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1314464902730607</v>
+        <v>0.1323647318113298</v>
       </c>
       <c r="T21">
-        <v>1.97797899013997</v>
+        <v>1.999185492178517</v>
       </c>
       <c r="U21">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V21">
         <v>0.17</v>
       </c>
       <c r="W21">
-        <v>0.045899</v>
+        <v>0.047974</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y21">
-        <v>4.534285158382353</v>
+        <v>4.121257280200984</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3180,22 +3180,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1154865854490638</v>
+        <v>0.1159965037769485</v>
       </c>
       <c r="C22">
-        <v>24.08199099434744</v>
+        <v>23.61365185293752</v>
       </c>
       <c r="D22">
-        <v>24.01919099434744</v>
+        <v>23.84471185293752</v>
       </c>
       <c r="E22">
-        <v>5.2912</v>
+        <v>5.58506</v>
       </c>
       <c r="F22">
-        <v>5.8772</v>
+        <v>6.171060000000001</v>
       </c>
       <c r="G22">
         <v>5.94</v>
@@ -3216,45 +3216,45 @@
         <v>1.4</v>
       </c>
       <c r="M22">
-        <v>0.33970216</v>
+        <v>0.378285978</v>
       </c>
       <c r="N22">
-        <v>1.06029784</v>
+        <v>1.021714022</v>
       </c>
       <c r="O22">
-        <v>0.1802506328</v>
+        <v>0.17369138374</v>
       </c>
       <c r="P22">
-        <v>0.8800472071999998</v>
+        <v>0.8480226382599998</v>
       </c>
       <c r="Q22">
-        <v>1.6400472072</v>
+        <v>1.60802263826</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1323647318113298</v>
+        <v>0.1333062199708209</v>
       </c>
       <c r="T22">
-        <v>1.999185492178517</v>
+        <v>2.020928867686395</v>
       </c>
       <c r="U22">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V22">
         <v>0.17</v>
       </c>
       <c r="W22">
-        <v>0.047974</v>
+        <v>0.050879</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>4.121257280200984</v>
+        <v>3.70090376440017</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3262,22 +3262,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1159965037769485</v>
+        <v>0.1159254221048332</v>
       </c>
       <c r="C23">
-        <v>23.61365185293753</v>
+        <v>23.34396171799847</v>
       </c>
       <c r="D23">
-        <v>23.84471185293753</v>
+        <v>23.86888171799847</v>
       </c>
       <c r="E23">
-        <v>5.585059999999999</v>
+        <v>5.87892</v>
       </c>
       <c r="F23">
-        <v>6.17106</v>
+        <v>6.46492</v>
       </c>
       <c r="G23">
         <v>5.94</v>
@@ -3298,28 +3298,28 @@
         <v>1.4</v>
       </c>
       <c r="M23">
-        <v>0.378285978</v>
+        <v>0.396299596</v>
       </c>
       <c r="N23">
-        <v>1.021714022</v>
+        <v>1.003700404</v>
       </c>
       <c r="O23">
-        <v>0.17369138374</v>
+        <v>0.17062906868</v>
       </c>
       <c r="P23">
-        <v>0.8480226382599998</v>
+        <v>0.8330713353199999</v>
       </c>
       <c r="Q23">
-        <v>1.60802263826</v>
+        <v>1.59307133532</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1333062199708209</v>
+        <v>0.1342718488523502</v>
       </c>
       <c r="T23">
-        <v>2.020928867686395</v>
+        <v>2.043229765643192</v>
       </c>
       <c r="U23">
         <v>0.0613</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.70090376440017</v>
+        <v>3.532680866018344</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3344,22 +3344,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1159254221048332</v>
+        <v>0.1163888604327178</v>
       </c>
       <c r="C24">
-        <v>23.34396171799847</v>
+        <v>22.8933949151962</v>
       </c>
       <c r="D24">
-        <v>23.86888171799847</v>
+        <v>23.7121749151962</v>
       </c>
       <c r="E24">
-        <v>5.87892</v>
+        <v>6.172779999999999</v>
       </c>
       <c r="F24">
-        <v>6.46492</v>
+        <v>6.75878</v>
       </c>
       <c r="G24">
         <v>5.94</v>
@@ -3380,45 +3380,45 @@
         <v>1.4</v>
       </c>
       <c r="M24">
-        <v>0.396299596</v>
+        <v>0.433237798</v>
       </c>
       <c r="N24">
-        <v>1.003700404</v>
+        <v>0.966762202</v>
       </c>
       <c r="O24">
-        <v>0.17062906868</v>
+        <v>0.16434957434</v>
       </c>
       <c r="P24">
-        <v>0.8330713353199999</v>
+        <v>0.80241262766</v>
       </c>
       <c r="Q24">
-        <v>1.59307133532</v>
+        <v>1.56241262766</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1342718488523502</v>
+        <v>0.1352625590035297</v>
       </c>
       <c r="T24">
-        <v>2.043229765643192</v>
+        <v>2.066109907702764</v>
       </c>
       <c r="U24">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V24">
         <v>0.17</v>
       </c>
       <c r="W24">
-        <v>0.050879</v>
+        <v>0.053203</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.532680866018344</v>
+        <v>3.231481663102719</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3426,22 +3426,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1163888604327178</v>
+        <v>0.1163410187606025</v>
       </c>
       <c r="C25">
-        <v>22.8933949151962</v>
+        <v>22.61561676540714</v>
       </c>
       <c r="D25">
-        <v>23.7121749151962</v>
+        <v>23.72825676540714</v>
       </c>
       <c r="E25">
-        <v>6.172779999999999</v>
+        <v>6.46664</v>
       </c>
       <c r="F25">
-        <v>6.75878</v>
+        <v>7.05264</v>
       </c>
       <c r="G25">
         <v>5.94</v>
@@ -3462,28 +3462,28 @@
         <v>1.4</v>
       </c>
       <c r="M25">
-        <v>0.433237798</v>
+        <v>0.452074224</v>
       </c>
       <c r="N25">
-        <v>0.966762202</v>
+        <v>0.9479257759999999</v>
       </c>
       <c r="O25">
-        <v>0.16434957434</v>
+        <v>0.16114738192</v>
       </c>
       <c r="P25">
-        <v>0.80241262766</v>
+        <v>0.7867783940799999</v>
       </c>
       <c r="Q25">
-        <v>1.56241262766</v>
+        <v>1.54677839408</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1352625590035297</v>
+        <v>0.136279340474477</v>
       </c>
       <c r="T25">
-        <v>2.066109907702764</v>
+        <v>2.089592158763903</v>
       </c>
       <c r="U25">
         <v>0.0641</v>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>3.231481663102719</v>
+        <v>3.096836593806772</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3508,22 +3508,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1163410187606025</v>
+        <v>0.1179116770884872</v>
       </c>
       <c r="C26">
-        <v>22.61561676540714</v>
+        <v>21.80493361554418</v>
       </c>
       <c r="D26">
-        <v>23.72825676540714</v>
+        <v>23.21143361554418</v>
       </c>
       <c r="E26">
-        <v>6.466639999999999</v>
+        <v>6.7605</v>
       </c>
       <c r="F26">
-        <v>7.052639999999999</v>
+        <v>7.3465</v>
       </c>
       <c r="G26">
         <v>5.94</v>
@@ -3544,45 +3544,45 @@
         <v>1.4</v>
       </c>
       <c r="M26">
-        <v>0.452074224</v>
+        <v>0.52821335</v>
       </c>
       <c r="N26">
-        <v>0.9479257759999999</v>
+        <v>0.8717866499999999</v>
       </c>
       <c r="O26">
-        <v>0.16114738192</v>
+        <v>0.1482037305</v>
       </c>
       <c r="P26">
-        <v>0.7867783940799999</v>
+        <v>0.7235829194999999</v>
       </c>
       <c r="Q26">
-        <v>1.54677839408</v>
+        <v>1.4835829195</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.136279340474477</v>
+        <v>0.1373232361179829</v>
       </c>
       <c r="T26">
-        <v>2.089592158763903</v>
+        <v>2.113700603186672</v>
       </c>
       <c r="U26">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V26">
         <v>0.17</v>
       </c>
       <c r="W26">
-        <v>0.053203</v>
+        <v>0.059677</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y26">
-        <v>3.096836593806773</v>
+        <v>2.650444181314236</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3590,22 +3590,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1179116770884872</v>
+        <v>0.1179285754163718</v>
       </c>
       <c r="C27">
-        <v>21.80493361554418</v>
+        <v>21.50563562631945</v>
       </c>
       <c r="D27">
-        <v>23.21143361554418</v>
+        <v>23.20599562631945</v>
       </c>
       <c r="E27">
-        <v>6.7605</v>
+        <v>7.05436</v>
       </c>
       <c r="F27">
-        <v>7.3465</v>
+        <v>7.64036</v>
       </c>
       <c r="G27">
         <v>5.94</v>
@@ -3626,28 +3626,28 @@
         <v>1.4</v>
       </c>
       <c r="M27">
-        <v>0.52821335</v>
+        <v>0.5493418840000001</v>
       </c>
       <c r="N27">
-        <v>0.8717866499999999</v>
+        <v>0.8506581159999999</v>
       </c>
       <c r="O27">
-        <v>0.1482037305</v>
+        <v>0.14461187972</v>
       </c>
       <c r="P27">
-        <v>0.7235829194999999</v>
+        <v>0.7060462362799999</v>
       </c>
       <c r="Q27">
-        <v>1.4835829195</v>
+        <v>1.46604623628</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1373232361179829</v>
+        <v>0.1383953451572592</v>
       </c>
       <c r="T27">
-        <v>2.113700603186672</v>
+        <v>2.138460627188436</v>
       </c>
       <c r="U27">
         <v>0.07190000000000001</v>
@@ -3664,7 +3664,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.650444181314236</v>
+        <v>2.548504020494457</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3672,22 +3672,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1179285754163718</v>
+        <v>0.1188194637442565</v>
       </c>
       <c r="C28">
-        <v>21.50563562631945</v>
+        <v>20.92864631284163</v>
       </c>
       <c r="D28">
-        <v>23.20599562631945</v>
+        <v>22.92286631284162</v>
       </c>
       <c r="E28">
-        <v>7.05436</v>
+        <v>7.34822</v>
       </c>
       <c r="F28">
-        <v>7.64036</v>
+        <v>7.934220000000001</v>
       </c>
       <c r="G28">
         <v>5.94</v>
@@ -3708,45 +3708,45 @@
         <v>1.4</v>
       </c>
       <c r="M28">
-        <v>0.5493418840000001</v>
+        <v>0.6014138760000001</v>
       </c>
       <c r="N28">
-        <v>0.8506581159999999</v>
+        <v>0.7985861239999998</v>
       </c>
       <c r="O28">
-        <v>0.14461187972</v>
+        <v>0.13575964108</v>
       </c>
       <c r="P28">
-        <v>0.7060462362799999</v>
+        <v>0.6628264829199999</v>
       </c>
       <c r="Q28">
-        <v>1.46604623628</v>
+        <v>1.42282648292</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1383953451572592</v>
+        <v>0.1394968270469267</v>
       </c>
       <c r="T28">
-        <v>2.138460627188436</v>
+        <v>2.163899008012165</v>
       </c>
       <c r="U28">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V28">
         <v>0.17</v>
       </c>
       <c r="W28">
-        <v>0.059677</v>
+        <v>0.062914</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y28">
-        <v>2.548504020494457</v>
+        <v>2.327847852981696</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3754,22 +3754,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1188194637442565</v>
+        <v>0.1188687320721412</v>
       </c>
       <c r="C29">
-        <v>20.92864631284163</v>
+        <v>20.61933002584265</v>
       </c>
       <c r="D29">
-        <v>22.92286631284162</v>
+        <v>22.90741002584265</v>
       </c>
       <c r="E29">
-        <v>7.34822</v>
+        <v>7.64208</v>
       </c>
       <c r="F29">
-        <v>7.934220000000001</v>
+        <v>8.22808</v>
       </c>
       <c r="G29">
         <v>5.94</v>
@@ -3790,28 +3790,28 @@
         <v>1.4</v>
       </c>
       <c r="M29">
-        <v>0.6014138760000001</v>
+        <v>0.6236884640000001</v>
       </c>
       <c r="N29">
-        <v>0.7985861239999998</v>
+        <v>0.7763115359999998</v>
       </c>
       <c r="O29">
-        <v>0.13575964108</v>
+        <v>0.13197296112</v>
       </c>
       <c r="P29">
-        <v>0.6628264829199999</v>
+        <v>0.6443385748799998</v>
       </c>
       <c r="Q29">
-        <v>1.42282648292</v>
+        <v>1.40433857488</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1394968270469267</v>
+        <v>0.1406289056557516</v>
       </c>
       <c r="T29">
-        <v>2.163899008012165</v>
+        <v>2.190044010525443</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.327847852981696</v>
+        <v>2.244710429660921</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3836,22 +3836,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1188687320721412</v>
+        <v>0.1189180004000259</v>
       </c>
       <c r="C30">
-        <v>20.61933002584265</v>
+        <v>20.31003456833605</v>
       </c>
       <c r="D30">
-        <v>22.90741002584265</v>
+        <v>22.89197456833605</v>
       </c>
       <c r="E30">
-        <v>7.64208</v>
+        <v>7.93594</v>
       </c>
       <c r="F30">
-        <v>8.22808</v>
+        <v>8.521940000000001</v>
       </c>
       <c r="G30">
         <v>5.94</v>
@@ -3872,28 +3872,28 @@
         <v>1.4</v>
       </c>
       <c r="M30">
-        <v>0.6236884640000001</v>
+        <v>0.6459630520000001</v>
       </c>
       <c r="N30">
-        <v>0.7763115359999998</v>
+        <v>0.7540369479999998</v>
       </c>
       <c r="O30">
-        <v>0.13197296112</v>
+        <v>0.12818628116</v>
       </c>
       <c r="P30">
-        <v>0.6443385748799998</v>
+        <v>0.6258506668399998</v>
       </c>
       <c r="Q30">
-        <v>1.40433857488</v>
+        <v>1.38585066684</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1406289056557516</v>
+        <v>0.1417928738028533</v>
       </c>
       <c r="T30">
-        <v>2.190044010525443</v>
+        <v>2.216925491982756</v>
       </c>
       <c r="U30">
         <v>0.07580000000000001</v>
@@ -3910,7 +3910,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>2.244710429660921</v>
+        <v>2.167306621741578</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3918,22 +3918,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1189180004000258</v>
+        <v>0.1189672687279105</v>
       </c>
       <c r="C31">
-        <v>20.31003456833607</v>
+        <v>20.00075989824424</v>
       </c>
       <c r="D31">
-        <v>22.89197456833607</v>
+        <v>22.87655989824424</v>
       </c>
       <c r="E31">
-        <v>7.935939999999999</v>
+        <v>8.229799999999999</v>
       </c>
       <c r="F31">
-        <v>8.521939999999999</v>
+        <v>8.815799999999999</v>
       </c>
       <c r="G31">
         <v>5.94</v>
@@ -3954,28 +3954,28 @@
         <v>1.4</v>
       </c>
       <c r="M31">
-        <v>0.6459630519999999</v>
+        <v>0.66823764</v>
       </c>
       <c r="N31">
-        <v>0.754036948</v>
+        <v>0.7317623599999999</v>
       </c>
       <c r="O31">
-        <v>0.12818628116</v>
+        <v>0.1243996012</v>
       </c>
       <c r="P31">
-        <v>0.62585066684</v>
+        <v>0.6073627587999999</v>
       </c>
       <c r="Q31">
-        <v>1.38585066684</v>
+        <v>1.3673627588</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1417928738028533</v>
+        <v>0.1429900981827293</v>
       </c>
       <c r="T31">
-        <v>2.216925491982756</v>
+        <v>2.244575015767421</v>
       </c>
       <c r="U31">
         <v>0.07580000000000001</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>2.167306621741579</v>
+        <v>2.095063067683526</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4000,22 +4000,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1189672687279105</v>
+        <v>0.1190165370557952</v>
       </c>
       <c r="C32">
-        <v>20.00075989824424</v>
+        <v>19.69150597360286</v>
       </c>
       <c r="D32">
-        <v>22.87655989824424</v>
+        <v>22.86116597360286</v>
       </c>
       <c r="E32">
-        <v>8.229799999999999</v>
+        <v>8.52366</v>
       </c>
       <c r="F32">
-        <v>8.815799999999999</v>
+        <v>9.10966</v>
       </c>
       <c r="G32">
         <v>5.94</v>
@@ -4036,28 +4036,28 @@
         <v>1.4</v>
       </c>
       <c r="M32">
-        <v>0.66823764</v>
+        <v>0.690512228</v>
       </c>
       <c r="N32">
-        <v>0.7317623599999999</v>
+        <v>0.7094877719999999</v>
       </c>
       <c r="O32">
-        <v>0.1243996012</v>
+        <v>0.12061292124</v>
       </c>
       <c r="P32">
-        <v>0.6073627587999999</v>
+        <v>0.5888748507599999</v>
       </c>
       <c r="Q32">
-        <v>1.3673627588</v>
+        <v>1.34887485076</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1429900981827293</v>
+        <v>0.1442220247185438</v>
       </c>
       <c r="T32">
-        <v>2.244575015767421</v>
+        <v>2.273025975024106</v>
       </c>
       <c r="U32">
         <v>0.07580000000000001</v>
@@ -4074,7 +4074,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>2.095063067683526</v>
+        <v>2.027480388080832</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4082,22 +4082,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1190165370557952</v>
+        <v>0.1228373253836798</v>
       </c>
       <c r="C33">
-        <v>19.69150597360286</v>
+        <v>18.26381019102934</v>
       </c>
       <c r="D33">
-        <v>22.86116597360286</v>
+        <v>21.72733019102933</v>
       </c>
       <c r="E33">
-        <v>8.52366</v>
+        <v>8.81752</v>
       </c>
       <c r="F33">
-        <v>9.10966</v>
+        <v>9.40352</v>
       </c>
       <c r="G33">
         <v>5.94</v>
@@ -4118,45 +4118,45 @@
         <v>1.4</v>
       </c>
       <c r="M33">
-        <v>0.690512228</v>
+        <v>0.8463168</v>
       </c>
       <c r="N33">
-        <v>0.7094877719999999</v>
+        <v>0.5536831999999999</v>
       </c>
       <c r="O33">
-        <v>0.12061292124</v>
+        <v>0.09412614399999999</v>
       </c>
       <c r="P33">
-        <v>0.5888748507599999</v>
+        <v>0.459557056</v>
       </c>
       <c r="Q33">
-        <v>1.34887485076</v>
+        <v>1.219557056</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1442220247185438</v>
+        <v>0.1454901843877645</v>
       </c>
       <c r="T33">
-        <v>2.273025975024106</v>
+        <v>2.302313727200104</v>
       </c>
       <c r="U33">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V33">
         <v>0.17</v>
       </c>
       <c r="W33">
-        <v>0.062914</v>
+        <v>0.07469999999999999</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>2.027480388080832</v>
+        <v>1.654226880525118</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4164,22 +4164,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1228373253836798</v>
+        <v>0.1230044537115645</v>
       </c>
       <c r="C34">
-        <v>18.26381019102934</v>
+        <v>17.92291595673773</v>
       </c>
       <c r="D34">
-        <v>21.72733019102933</v>
+        <v>21.68029595673773</v>
       </c>
       <c r="E34">
-        <v>8.81752</v>
+        <v>9.11138</v>
       </c>
       <c r="F34">
-        <v>9.40352</v>
+        <v>9.697380000000001</v>
       </c>
       <c r="G34">
         <v>5.94</v>
@@ -4200,28 +4200,28 @@
         <v>1.4</v>
       </c>
       <c r="M34">
-        <v>0.8463168</v>
+        <v>0.8727642</v>
       </c>
       <c r="N34">
-        <v>0.5536831999999999</v>
+        <v>0.5272357999999999</v>
       </c>
       <c r="O34">
-        <v>0.09412614399999999</v>
+        <v>0.089630086</v>
       </c>
       <c r="P34">
-        <v>0.459557056</v>
+        <v>0.4376057139999999</v>
       </c>
       <c r="Q34">
-        <v>1.219557056</v>
+        <v>1.197605714</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1454901843877645</v>
+        <v>0.1467961995694993</v>
       </c>
       <c r="T34">
-        <v>2.302313727200104</v>
+        <v>2.332475740635088</v>
       </c>
       <c r="U34">
         <v>0.09</v>
@@ -4238,7 +4238,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>1.654226880525118</v>
+        <v>1.604098793236478</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4246,22 +4246,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1230044537115645</v>
+        <v>0.1231715820394492</v>
       </c>
       <c r="C35">
-        <v>17.92291595673773</v>
+        <v>17.58222491728132</v>
       </c>
       <c r="D35">
-        <v>21.68029595673773</v>
+        <v>21.63346491728132</v>
       </c>
       <c r="E35">
-        <v>9.11138</v>
+        <v>9.405240000000001</v>
       </c>
       <c r="F35">
-        <v>9.697380000000001</v>
+        <v>9.991240000000001</v>
       </c>
       <c r="G35">
         <v>5.94</v>
@@ -4282,28 +4282,28 @@
         <v>1.4</v>
       </c>
       <c r="M35">
-        <v>0.8727642</v>
+        <v>0.8992116000000001</v>
       </c>
       <c r="N35">
-        <v>0.5272357999999999</v>
+        <v>0.5007883999999998</v>
       </c>
       <c r="O35">
-        <v>0.089630086</v>
+        <v>0.08513402799999997</v>
       </c>
       <c r="P35">
-        <v>0.4376057139999999</v>
+        <v>0.4156543719999998</v>
       </c>
       <c r="Q35">
-        <v>1.197605714</v>
+        <v>1.175654372</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1467961995694993</v>
+        <v>0.1481417909688625</v>
       </c>
       <c r="T35">
-        <v>2.332475740635088</v>
+        <v>2.363551754477193</v>
       </c>
       <c r="U35">
         <v>0.09</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>1.604098793236478</v>
+        <v>1.556919416964816</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4328,22 +4328,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1231715820394492</v>
+        <v>0.1233387103673339</v>
       </c>
       <c r="C36">
-        <v>17.58222491728132</v>
+        <v>17.24173575875072</v>
       </c>
       <c r="D36">
-        <v>21.63346491728132</v>
+        <v>21.58683575875072</v>
       </c>
       <c r="E36">
-        <v>9.405240000000001</v>
+        <v>9.6991</v>
       </c>
       <c r="F36">
-        <v>9.991240000000001</v>
+        <v>10.2851</v>
       </c>
       <c r="G36">
         <v>5.94</v>
@@ -4364,28 +4364,28 @@
         <v>1.4</v>
       </c>
       <c r="M36">
-        <v>0.8992116000000001</v>
+        <v>0.925659</v>
       </c>
       <c r="N36">
-        <v>0.5007883999999998</v>
+        <v>0.4743409999999999</v>
       </c>
       <c r="O36">
-        <v>0.08513402799999997</v>
+        <v>0.08063796999999999</v>
       </c>
       <c r="P36">
-        <v>0.4156543719999998</v>
+        <v>0.3937030299999999</v>
       </c>
       <c r="Q36">
-        <v>1.175654372</v>
+        <v>1.15370303</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1481417909688625</v>
+        <v>0.1495287851805137</v>
       </c>
       <c r="T36">
-        <v>2.363551754477193</v>
+        <v>2.395583953360593</v>
       </c>
       <c r="U36">
         <v>0.09</v>
@@ -4402,7 +4402,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>1.556919416964816</v>
+        <v>1.512436005051536</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4410,22 +4410,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1233387103673339</v>
+        <v>0.1417949620921898</v>
       </c>
       <c r="C37">
-        <v>17.24173575875072</v>
+        <v>12.79753217796984</v>
       </c>
       <c r="D37">
-        <v>21.58683575875072</v>
+        <v>17.43649217796984</v>
       </c>
       <c r="E37">
-        <v>9.6991</v>
+        <v>9.99296</v>
       </c>
       <c r="F37">
-        <v>10.2851</v>
+        <v>10.57896</v>
       </c>
       <c r="G37">
         <v>5.94</v>
@@ -4446,45 +4446,45 @@
         <v>1.4</v>
       </c>
       <c r="M37">
-        <v>0.925659</v>
+        <v>1.552991328</v>
       </c>
       <c r="N37">
-        <v>0.4743409999999999</v>
+        <v>-0.1529913280000004</v>
       </c>
       <c r="O37">
-        <v>0.08063796999999999</v>
+        <v>-0.02600852576000006</v>
       </c>
       <c r="P37">
-        <v>0.3937030299999999</v>
+        <v>-0.1269828022400003</v>
       </c>
       <c r="Q37">
-        <v>1.15370303</v>
+        <v>0.6330171977599999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1495287851805137</v>
+        <v>0.1516344639050636</v>
       </c>
       <c r="T37">
-        <v>2.395583953360593</v>
+        <v>2.444213946999161</v>
       </c>
       <c r="U37">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V37">
-        <v>0.17</v>
+        <v>0.1532526265336621</v>
       </c>
       <c r="W37">
-        <v>0.07469999999999999</v>
+        <v>0.1243025144248584</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y37">
-        <v>1.512436005051536</v>
+        <v>0.9014860384333064</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4492,22 +4492,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1417949620921898</v>
+        <v>0.1428049620921898</v>
       </c>
       <c r="C38">
-        <v>12.79753217796984</v>
+        <v>12.322126237227</v>
       </c>
       <c r="D38">
-        <v>17.43649217796984</v>
+        <v>17.254946237227</v>
       </c>
       <c r="E38">
-        <v>9.992959999999998</v>
+        <v>10.28682</v>
       </c>
       <c r="F38">
-        <v>10.57896</v>
+        <v>10.87282</v>
       </c>
       <c r="G38">
         <v>5.94</v>
@@ -4528,37 +4528,37 @@
         <v>1.4</v>
       </c>
       <c r="M38">
-        <v>1.552991328</v>
+        <v>1.596129976</v>
       </c>
       <c r="N38">
-        <v>-0.1529913279999999</v>
+        <v>-0.1961299760000002</v>
       </c>
       <c r="O38">
-        <v>-0.02600852575999999</v>
+        <v>-0.03334209592000003</v>
       </c>
       <c r="P38">
-        <v>-0.1269828022399999</v>
+        <v>-0.1627878800800001</v>
       </c>
       <c r="Q38">
-        <v>0.6330171977600003</v>
+        <v>0.5972121199200001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1516344639050636</v>
+        <v>0.1533143760305408</v>
       </c>
       <c r="T38">
-        <v>2.44421394699916</v>
+        <v>2.483010993776925</v>
       </c>
       <c r="U38">
         <v>0.1468</v>
       </c>
       <c r="V38">
-        <v>0.1532526265336622</v>
+        <v>0.149110663654374</v>
       </c>
       <c r="W38">
-        <v>0.1243025144248584</v>
+        <v>0.1249105545755379</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4566,7 +4566,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.9014860384333068</v>
+        <v>0.8771215509080821</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4574,22 +4574,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1428049620921898</v>
+        <v>0.1438149620921897</v>
       </c>
       <c r="C39">
-        <v>12.322126237227</v>
+        <v>11.85046179464397</v>
       </c>
       <c r="D39">
-        <v>17.254946237227</v>
+        <v>17.07714179464397</v>
       </c>
       <c r="E39">
-        <v>10.28682</v>
+        <v>10.58068</v>
       </c>
       <c r="F39">
-        <v>10.87282</v>
+        <v>11.16668</v>
       </c>
       <c r="G39">
         <v>5.94</v>
@@ -4610,37 +4610,37 @@
         <v>1.4</v>
       </c>
       <c r="M39">
-        <v>1.596129976</v>
+        <v>1.639268624</v>
       </c>
       <c r="N39">
-        <v>-0.1961299760000002</v>
+        <v>-0.2392686240000002</v>
       </c>
       <c r="O39">
-        <v>-0.03334209592000003</v>
+        <v>-0.04067566608000003</v>
       </c>
       <c r="P39">
-        <v>-0.1627878800800001</v>
+        <v>-0.1985929579200001</v>
       </c>
       <c r="Q39">
-        <v>0.5972121199200001</v>
+        <v>0.5614070420800001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1533143760305408</v>
+        <v>0.1550484788697431</v>
       </c>
       <c r="T39">
-        <v>2.483010993776925</v>
+        <v>2.523059558192682</v>
       </c>
       <c r="U39">
         <v>0.1468</v>
       </c>
       <c r="V39">
-        <v>0.149110663654374</v>
+        <v>0.1451866988213641</v>
       </c>
       <c r="W39">
-        <v>0.1249105545755379</v>
+        <v>0.1254865926130238</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.8771215509080821</v>
+        <v>0.8540394048315536</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4656,22 +4656,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1438149620921897</v>
+        <v>0.1448249620921898</v>
       </c>
       <c r="C40">
-        <v>11.85046179464397</v>
+        <v>11.38242436656747</v>
       </c>
       <c r="D40">
-        <v>17.07714179464397</v>
+        <v>16.90296436656747</v>
       </c>
       <c r="E40">
-        <v>10.58068</v>
+        <v>10.87454</v>
       </c>
       <c r="F40">
-        <v>11.16668</v>
+        <v>11.46054</v>
       </c>
       <c r="G40">
         <v>5.94</v>
@@ -4692,37 +4692,37 @@
         <v>1.4</v>
       </c>
       <c r="M40">
-        <v>1.639268624</v>
+        <v>1.682407272</v>
       </c>
       <c r="N40">
-        <v>-0.2392686240000002</v>
+        <v>-0.2824072720000002</v>
       </c>
       <c r="O40">
-        <v>-0.04067566608000003</v>
+        <v>-0.04800923624000003</v>
       </c>
       <c r="P40">
-        <v>-0.1985929579200001</v>
+        <v>-0.2343980357600001</v>
       </c>
       <c r="Q40">
-        <v>0.5614070420800001</v>
+        <v>0.5256019642400001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1550484788697431</v>
+        <v>0.1568394375397389</v>
       </c>
       <c r="T40">
-        <v>2.523059558192682</v>
+        <v>2.564421190294201</v>
       </c>
       <c r="U40">
         <v>0.1468</v>
       </c>
       <c r="V40">
-        <v>0.1451866988213641</v>
+        <v>0.1414639629541497</v>
       </c>
       <c r="W40">
-        <v>0.1254865926130238</v>
+        <v>0.1260330902383308</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.8540394048315536</v>
+        <v>0.8321409585538215</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4738,22 +4738,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1448249620921898</v>
+        <v>0.1458349620921897</v>
       </c>
       <c r="C41">
-        <v>11.38242436656747</v>
+        <v>10.91790409286736</v>
       </c>
       <c r="D41">
-        <v>16.90296436656747</v>
+        <v>16.73230409286736</v>
       </c>
       <c r="E41">
-        <v>10.87454</v>
+        <v>11.1684</v>
       </c>
       <c r="F41">
-        <v>11.46054</v>
+        <v>11.7544</v>
       </c>
       <c r="G41">
         <v>5.94</v>
@@ -4774,37 +4774,37 @@
         <v>1.4</v>
       </c>
       <c r="M41">
-        <v>1.682407272</v>
+        <v>1.72554592</v>
       </c>
       <c r="N41">
-        <v>-0.2824072720000002</v>
+        <v>-0.3255459200000004</v>
       </c>
       <c r="O41">
-        <v>-0.04800923624000003</v>
+        <v>-0.05534280640000007</v>
       </c>
       <c r="P41">
-        <v>-0.2343980357600001</v>
+        <v>-0.2702031136000003</v>
       </c>
       <c r="Q41">
-        <v>0.5256019642400001</v>
+        <v>0.4897968863999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1568394375397389</v>
+        <v>0.1586900948320679</v>
       </c>
       <c r="T41">
-        <v>2.564421190294201</v>
+        <v>2.607161543465771</v>
       </c>
       <c r="U41">
         <v>0.1468</v>
       </c>
       <c r="V41">
-        <v>0.1414639629541497</v>
+        <v>0.1379273638802959</v>
       </c>
       <c r="W41">
-        <v>0.1260330902383308</v>
+        <v>0.1265522629823726</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.8321409585538215</v>
+        <v>0.8113374345899759</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4820,22 +4820,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1458349620921897</v>
+        <v>0.1700486012733401</v>
       </c>
       <c r="C42">
-        <v>10.91790409286736</v>
+        <v>7.363243006803872</v>
       </c>
       <c r="D42">
-        <v>16.73230409286736</v>
+        <v>13.47150300680387</v>
       </c>
       <c r="E42">
-        <v>11.1684</v>
+        <v>11.46226</v>
       </c>
       <c r="F42">
-        <v>11.7544</v>
+        <v>12.04826</v>
       </c>
       <c r="G42">
         <v>5.94</v>
@@ -4856,45 +4856,45 @@
         <v>1.4</v>
       </c>
       <c r="M42">
-        <v>1.72554592</v>
+        <v>2.419290608</v>
       </c>
       <c r="N42">
-        <v>-0.3255459200000004</v>
+        <v>-1.019290608</v>
       </c>
       <c r="O42">
-        <v>-0.05534280640000007</v>
+        <v>-0.1732794033600001</v>
       </c>
       <c r="P42">
-        <v>-0.2702031136000003</v>
+        <v>-0.8460112046400003</v>
       </c>
       <c r="Q42">
-        <v>0.4897968863999999</v>
+        <v>-0.08601120464000012</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1586900948320679</v>
+        <v>0.1624062645430358</v>
       </c>
       <c r="T42">
-        <v>2.607161543465771</v>
+        <v>2.692985324319535</v>
       </c>
       <c r="U42">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V42">
-        <v>0.1379273638802959</v>
+        <v>0.09837594508613079</v>
       </c>
       <c r="W42">
-        <v>0.1265522629823726</v>
+        <v>0.1810461102267049</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y42">
-        <v>0.8113374345899759</v>
+        <v>0.5786820299184163</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4902,22 +4902,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1700486012733401</v>
+        <v>0.1715986012733401</v>
       </c>
       <c r="C43">
-        <v>7.363243006803872</v>
+        <v>6.903396823736738</v>
       </c>
       <c r="D43">
-        <v>13.47150300680387</v>
+        <v>13.30551682373674</v>
       </c>
       <c r="E43">
-        <v>11.46226</v>
+        <v>11.75612</v>
       </c>
       <c r="F43">
-        <v>12.04826</v>
+        <v>12.34212</v>
       </c>
       <c r="G43">
         <v>5.94</v>
@@ -4938,37 +4938,37 @@
         <v>1.4</v>
       </c>
       <c r="M43">
-        <v>2.419290608</v>
+        <v>2.478297696</v>
       </c>
       <c r="N43">
-        <v>-1.019290608</v>
+        <v>-1.078297696</v>
       </c>
       <c r="O43">
-        <v>-0.1732794033600001</v>
+        <v>-0.1833106083200001</v>
       </c>
       <c r="P43">
-        <v>-0.8460112046400003</v>
+        <v>-0.8949870876800003</v>
       </c>
       <c r="Q43">
-        <v>-0.08601120464000012</v>
+        <v>-0.1349870876800001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1624062645430358</v>
+        <v>0.1644167173799847</v>
       </c>
       <c r="T43">
-        <v>2.692985324319535</v>
+        <v>2.73941610577332</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
       </c>
       <c r="V43">
-        <v>0.09837594508613079</v>
+        <v>0.09603366067931815</v>
       </c>
       <c r="W43">
-        <v>0.1810461102267049</v>
+        <v>0.1815164409355929</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4976,7 +4976,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5786820299184163</v>
+        <v>0.5649038863489303</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4984,22 +4984,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1715986012733402</v>
+        <v>0.1731486012733402</v>
       </c>
       <c r="C44">
-        <v>6.90339682373674</v>
+        <v>6.447591181063164</v>
       </c>
       <c r="D44">
-        <v>13.30551682373674</v>
+        <v>13.14357118106316</v>
       </c>
       <c r="E44">
-        <v>11.75612</v>
+        <v>12.04998</v>
       </c>
       <c r="F44">
-        <v>12.34212</v>
+        <v>12.63598</v>
       </c>
       <c r="G44">
         <v>5.94</v>
@@ -5020,37 +5020,37 @@
         <v>1.4</v>
       </c>
       <c r="M44">
-        <v>2.478297696</v>
+        <v>2.537304784</v>
       </c>
       <c r="N44">
-        <v>-1.078297696</v>
+        <v>-1.137304784</v>
       </c>
       <c r="O44">
-        <v>-0.18331060832</v>
+        <v>-0.1933418132800001</v>
       </c>
       <c r="P44">
-        <v>-0.8949870876799999</v>
+        <v>-0.9439629707200002</v>
       </c>
       <c r="Q44">
-        <v>-0.1349870876799997</v>
+        <v>-0.18396297072</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1644167173799847</v>
+        <v>0.1664977124217388</v>
       </c>
       <c r="T44">
-        <v>2.73941610577332</v>
+        <v>2.787476037453553</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
       </c>
       <c r="V44">
-        <v>0.09603366067931818</v>
+        <v>0.09380031973328749</v>
       </c>
       <c r="W44">
-        <v>0.1815164409355929</v>
+        <v>0.1819648957975559</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5649038863489304</v>
+        <v>0.551766586666397</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5066,22 +5066,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1731486012733402</v>
+        <v>0.1746986012733402</v>
       </c>
       <c r="C45">
-        <v>6.447591181063164</v>
+        <v>5.995680316822623</v>
       </c>
       <c r="D45">
-        <v>13.14357118106316</v>
+        <v>12.98552031682262</v>
       </c>
       <c r="E45">
-        <v>12.04998</v>
+        <v>12.34384</v>
       </c>
       <c r="F45">
-        <v>12.63598</v>
+        <v>12.92984</v>
       </c>
       <c r="G45">
         <v>5.94</v>
@@ -5102,37 +5102,37 @@
         <v>1.4</v>
       </c>
       <c r="M45">
-        <v>2.537304784</v>
+        <v>2.596311872</v>
       </c>
       <c r="N45">
-        <v>-1.137304784</v>
+        <v>-1.196311872</v>
       </c>
       <c r="O45">
-        <v>-0.1933418132800001</v>
+        <v>-0.2033730182400001</v>
       </c>
       <c r="P45">
-        <v>-0.9439629707200002</v>
+        <v>-0.9929388537600002</v>
       </c>
       <c r="Q45">
-        <v>-0.18396297072</v>
+        <v>-0.23293885376</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1664977124217388</v>
+        <v>0.1686530287149842</v>
       </c>
       <c r="T45">
-        <v>2.787476037453553</v>
+        <v>2.837252395265224</v>
       </c>
       <c r="U45">
         <v>0.2008</v>
       </c>
       <c r="V45">
-        <v>0.09380031973328749</v>
+        <v>0.0916684942848037</v>
       </c>
       <c r="W45">
-        <v>0.1819648957975559</v>
+        <v>0.1823929663476114</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.551766586666397</v>
+        <v>0.5392264369694335</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5148,22 +5148,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1746986012733402</v>
+        <v>0.1762486012733402</v>
       </c>
       <c r="C46">
-        <v>5.995680316822623</v>
+        <v>5.547525396872507</v>
       </c>
       <c r="D46">
-        <v>12.98552031682262</v>
+        <v>12.8312253968725</v>
       </c>
       <c r="E46">
-        <v>12.34384</v>
+        <v>12.6377</v>
       </c>
       <c r="F46">
-        <v>12.92984</v>
+        <v>13.2237</v>
       </c>
       <c r="G46">
         <v>5.94</v>
@@ -5184,37 +5184,37 @@
         <v>1.4</v>
       </c>
       <c r="M46">
-        <v>2.596311872</v>
+        <v>2.65531896</v>
       </c>
       <c r="N46">
-        <v>-1.196311872</v>
+        <v>-1.25531896</v>
       </c>
       <c r="O46">
-        <v>-0.2033730182400001</v>
+        <v>-0.2134042232</v>
       </c>
       <c r="P46">
-        <v>-0.9929388537600002</v>
+        <v>-1.0419147368</v>
       </c>
       <c r="Q46">
-        <v>-0.23293885376</v>
+        <v>-0.2819147367999997</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1686530287149842</v>
+        <v>0.1708867201461657</v>
       </c>
       <c r="T46">
-        <v>2.837252395265224</v>
+        <v>2.888838802451864</v>
       </c>
       <c r="U46">
         <v>0.2008</v>
       </c>
       <c r="V46">
-        <v>0.0916684942848037</v>
+        <v>0.08963141663403029</v>
       </c>
       <c r="W46">
-        <v>0.1823929663476114</v>
+        <v>0.1828020115398867</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5222,7 +5222,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.5392264369694335</v>
+        <v>0.5272436272590018</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5230,22 +5230,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1762486012733402</v>
+        <v>0.1777986012733402</v>
       </c>
       <c r="C47">
-        <v>5.547525396872507</v>
+        <v>5.102994108136894</v>
       </c>
       <c r="D47">
-        <v>12.8312253968725</v>
+        <v>12.68055410813689</v>
       </c>
       <c r="E47">
-        <v>12.6377</v>
+        <v>12.93156</v>
       </c>
       <c r="F47">
-        <v>13.2237</v>
+        <v>13.51756</v>
       </c>
       <c r="G47">
         <v>5.94</v>
@@ -5266,37 +5266,37 @@
         <v>1.4</v>
       </c>
       <c r="M47">
-        <v>2.65531896</v>
+        <v>2.714326048</v>
       </c>
       <c r="N47">
-        <v>-1.25531896</v>
+        <v>-1.314326048</v>
       </c>
       <c r="O47">
-        <v>-0.2134042232</v>
+        <v>-0.2234354281600001</v>
       </c>
       <c r="P47">
-        <v>-1.0419147368</v>
+        <v>-1.09089061984</v>
       </c>
       <c r="Q47">
-        <v>-0.2819147367999997</v>
+        <v>-0.3308906198399999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1708867201461657</v>
+        <v>0.1732031408896132</v>
       </c>
       <c r="T47">
-        <v>2.888838802451864</v>
+        <v>2.942335817312084</v>
       </c>
       <c r="U47">
         <v>0.2008</v>
       </c>
       <c r="V47">
-        <v>0.08963141663403029</v>
+        <v>0.08768290757676876</v>
       </c>
       <c r="W47">
-        <v>0.1828020115398867</v>
+        <v>0.1831932721585848</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5304,7 +5304,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.5272436272590018</v>
+        <v>0.5157818092751103</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5312,22 +5312,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1777986012733402</v>
+        <v>0.1793486012733402</v>
       </c>
       <c r="C48">
-        <v>5.102994108136894</v>
+        <v>4.661960280180557</v>
       </c>
       <c r="D48">
-        <v>12.68055410813689</v>
+        <v>12.53338028018056</v>
       </c>
       <c r="E48">
-        <v>12.93156</v>
+        <v>13.22542</v>
       </c>
       <c r="F48">
-        <v>13.51756</v>
+        <v>13.81142</v>
       </c>
       <c r="G48">
         <v>5.94</v>
@@ -5348,37 +5348,37 @@
         <v>1.4</v>
       </c>
       <c r="M48">
-        <v>2.714326048</v>
+        <v>2.773333136</v>
       </c>
       <c r="N48">
-        <v>-1.314326048</v>
+        <v>-1.373333136</v>
       </c>
       <c r="O48">
-        <v>-0.2234354281600001</v>
+        <v>-0.2334666331200001</v>
       </c>
       <c r="P48">
-        <v>-1.09089061984</v>
+        <v>-1.13986650288</v>
       </c>
       <c r="Q48">
-        <v>-0.3308906198399999</v>
+        <v>-0.3798665028799999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1732031408896132</v>
+        <v>0.1756069737365871</v>
       </c>
       <c r="T48">
-        <v>2.942335817312084</v>
+        <v>2.997851587450048</v>
       </c>
       <c r="U48">
         <v>0.2008</v>
       </c>
       <c r="V48">
-        <v>0.08768290757676876</v>
+        <v>0.08581731379853964</v>
       </c>
       <c r="W48">
-        <v>0.1831932721585848</v>
+        <v>0.1835678833892533</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5386,7 +5386,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.5157818092751103</v>
+        <v>0.5048077282267036</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5394,22 +5394,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1793486012733402</v>
+        <v>0.1981277925302709</v>
       </c>
       <c r="C49">
-        <v>4.661960280180557</v>
+        <v>2.822966976088445</v>
       </c>
       <c r="D49">
-        <v>12.53338028018056</v>
+        <v>10.98824697608844</v>
       </c>
       <c r="E49">
-        <v>13.22542</v>
+        <v>13.51928</v>
       </c>
       <c r="F49">
-        <v>13.81142</v>
+        <v>14.10528</v>
       </c>
       <c r="G49">
         <v>5.94</v>
@@ -5430,45 +5430,45 @@
         <v>1.4</v>
       </c>
       <c r="M49">
-        <v>2.773333136</v>
+        <v>3.326025024</v>
       </c>
       <c r="N49">
-        <v>-1.373333136</v>
+        <v>-1.926025024</v>
       </c>
       <c r="O49">
-        <v>-0.2334666331200001</v>
+        <v>-0.3274242540800001</v>
       </c>
       <c r="P49">
-        <v>-1.13986650288</v>
+        <v>-1.59860076992</v>
       </c>
       <c r="Q49">
-        <v>-0.3798665028799999</v>
+        <v>-0.83860076992</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1756069737365871</v>
+        <v>0.1789286294948498</v>
       </c>
       <c r="T49">
-        <v>2.997851587450048</v>
+        <v>3.074564191566971</v>
       </c>
       <c r="U49">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.08581731379853964</v>
+        <v>0.0715568879616463</v>
       </c>
       <c r="W49">
-        <v>0.1835678833892533</v>
+        <v>0.2189268858186438</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y49">
-        <v>0.5048077282267036</v>
+        <v>0.4209228703626253</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5476,22 +5476,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1981277925302709</v>
+        <v>0.2000277925302709</v>
       </c>
       <c r="C50">
-        <v>2.822966976088447</v>
+        <v>2.393737929355378</v>
       </c>
       <c r="D50">
-        <v>10.98824697608845</v>
+        <v>10.85287792935538</v>
       </c>
       <c r="E50">
-        <v>13.51928</v>
+        <v>13.81314</v>
       </c>
       <c r="F50">
-        <v>14.10528</v>
+        <v>14.39914</v>
       </c>
       <c r="G50">
         <v>5.94</v>
@@ -5512,37 +5512,37 @@
         <v>1.4</v>
       </c>
       <c r="M50">
-        <v>3.326025024</v>
+        <v>3.395317212</v>
       </c>
       <c r="N50">
-        <v>-1.926025024</v>
+        <v>-1.995317212</v>
       </c>
       <c r="O50">
-        <v>-0.32742425408</v>
+        <v>-0.33920392604</v>
       </c>
       <c r="P50">
-        <v>-1.59860076992</v>
+        <v>-1.65611328596</v>
       </c>
       <c r="Q50">
-        <v>-0.8386007699199998</v>
+        <v>-0.8961132859599998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1789286294948498</v>
+        <v>0.1815389947790625</v>
       </c>
       <c r="T50">
-        <v>3.074564191566971</v>
+        <v>3.134849763950637</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.07155688796164632</v>
+        <v>0.07009654330936782</v>
       </c>
       <c r="W50">
-        <v>0.2189268858186438</v>
+        <v>0.2192712350876511</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.4209228703626254</v>
+        <v>0.4123326077021636</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5558,22 +5558,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.2000277925302709</v>
+        <v>0.2019277925302709</v>
       </c>
       <c r="C51">
-        <v>2.393737929355378</v>
+        <v>1.967803634756118</v>
       </c>
       <c r="D51">
-        <v>10.85287792935538</v>
+        <v>10.72080363475612</v>
       </c>
       <c r="E51">
-        <v>13.81314</v>
+        <v>14.107</v>
       </c>
       <c r="F51">
-        <v>14.39914</v>
+        <v>14.693</v>
       </c>
       <c r="G51">
         <v>5.94</v>
@@ -5594,37 +5594,37 @@
         <v>1.4</v>
       </c>
       <c r="M51">
-        <v>3.395317212</v>
+        <v>3.4646094</v>
       </c>
       <c r="N51">
-        <v>-1.995317212</v>
+        <v>-2.0646094</v>
       </c>
       <c r="O51">
-        <v>-0.33920392604</v>
+        <v>-0.3509835980000001</v>
       </c>
       <c r="P51">
-        <v>-1.65611328596</v>
+        <v>-1.713625802</v>
       </c>
       <c r="Q51">
-        <v>-0.8961132859599998</v>
+        <v>-0.9536258019999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1815389947790625</v>
+        <v>0.1842537746746438</v>
       </c>
       <c r="T51">
-        <v>3.134849763950637</v>
+        <v>3.19754675922965</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.07009654330936782</v>
+        <v>0.06869461244318047</v>
       </c>
       <c r="W51">
-        <v>0.2192712350876511</v>
+        <v>0.2196018103858981</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.4123326077021636</v>
+        <v>0.4040859555481203</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5640,22 +5640,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2019277925302709</v>
+        <v>0.2038277925302709</v>
       </c>
       <c r="C52">
-        <v>1.967803634756118</v>
+        <v>1.545045251883781</v>
       </c>
       <c r="D52">
-        <v>10.72080363475612</v>
+        <v>10.59190525188378</v>
       </c>
       <c r="E52">
-        <v>14.107</v>
+        <v>14.40086</v>
       </c>
       <c r="F52">
-        <v>14.693</v>
+        <v>14.98686</v>
       </c>
       <c r="G52">
         <v>5.94</v>
@@ -5676,37 +5676,37 @@
         <v>1.4</v>
       </c>
       <c r="M52">
-        <v>3.4646094</v>
+        <v>3.533901588</v>
       </c>
       <c r="N52">
-        <v>-2.0646094</v>
+        <v>-2.133901588</v>
       </c>
       <c r="O52">
-        <v>-0.3509835980000001</v>
+        <v>-0.36276326996</v>
       </c>
       <c r="P52">
-        <v>-1.713625802</v>
+        <v>-1.77113831804</v>
       </c>
       <c r="Q52">
-        <v>-0.9536258019999999</v>
+        <v>-1.01113831804</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1842537746746438</v>
+        <v>0.1870793619129018</v>
       </c>
       <c r="T52">
-        <v>3.19754675922965</v>
+        <v>3.262802815540459</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.06869461244318047</v>
+        <v>0.06734765925802007</v>
       </c>
       <c r="W52">
-        <v>0.2196018103858981</v>
+        <v>0.2199194219469589</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.4040859555481203</v>
+        <v>0.396162701517765</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5722,22 +5722,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2038277925302709</v>
+        <v>0.205727792530271</v>
       </c>
       <c r="C53">
-        <v>1.545045251883781</v>
+        <v>1.125349587799503</v>
       </c>
       <c r="D53">
-        <v>10.59190525188378</v>
+        <v>10.4660695877995</v>
       </c>
       <c r="E53">
-        <v>14.40086</v>
+        <v>14.69472</v>
       </c>
       <c r="F53">
-        <v>14.98686</v>
+        <v>15.28072</v>
       </c>
       <c r="G53">
         <v>5.94</v>
@@ -5758,37 +5758,37 @@
         <v>1.4</v>
       </c>
       <c r="M53">
-        <v>3.533901588</v>
+        <v>3.603193776</v>
       </c>
       <c r="N53">
-        <v>-2.133901588</v>
+        <v>-2.203193776</v>
       </c>
       <c r="O53">
-        <v>-0.36276326996</v>
+        <v>-0.3745429419200001</v>
       </c>
       <c r="P53">
-        <v>-1.77113831804</v>
+        <v>-1.82865083408</v>
       </c>
       <c r="Q53">
-        <v>-1.01113831804</v>
+        <v>-1.06865083408</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1870793619129018</v>
+        <v>0.190022681952754</v>
       </c>
       <c r="T53">
-        <v>3.262802815540459</v>
+        <v>3.330777874197552</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.06734765925802007</v>
+        <v>0.06605251196459659</v>
       </c>
       <c r="W53">
-        <v>0.2199194219469589</v>
+        <v>0.2202248176787481</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.396162701517765</v>
+        <v>0.3885441880270387</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5804,22 +5804,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.205727792530271</v>
+        <v>0.2076277925302709</v>
       </c>
       <c r="C54">
-        <v>1.125349587799503</v>
+        <v>0.7086087655013245</v>
       </c>
       <c r="D54">
-        <v>10.4660695877995</v>
+        <v>10.34318876550133</v>
       </c>
       <c r="E54">
-        <v>14.69472</v>
+        <v>14.98858</v>
       </c>
       <c r="F54">
-        <v>15.28072</v>
+        <v>15.57458</v>
       </c>
       <c r="G54">
         <v>5.94</v>
@@ -5840,37 +5840,37 @@
         <v>1.4</v>
       </c>
       <c r="M54">
-        <v>3.603193776</v>
+        <v>3.672485964</v>
       </c>
       <c r="N54">
-        <v>-2.203193776</v>
+        <v>-2.272485964</v>
       </c>
       <c r="O54">
-        <v>-0.3745429419200001</v>
+        <v>-0.3863226138800001</v>
       </c>
       <c r="P54">
-        <v>-1.82865083408</v>
+        <v>-1.88616335012</v>
       </c>
       <c r="Q54">
-        <v>-1.06865083408</v>
+        <v>-1.12616335012</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.190022681952754</v>
+        <v>0.1930912496538764</v>
       </c>
       <c r="T54">
-        <v>3.330777874197552</v>
+        <v>3.401645488542181</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.06605251196459659</v>
+        <v>0.06480623815394383</v>
       </c>
       <c r="W54">
-        <v>0.2202248176787481</v>
+        <v>0.2205186890433</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3885441880270387</v>
+        <v>0.3812131656114343</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5886,22 +5886,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2076277925302709</v>
+        <v>0.2095277925302709</v>
       </c>
       <c r="C55">
-        <v>0.7086087655013245</v>
+        <v>0.2947199154768594</v>
       </c>
       <c r="D55">
-        <v>10.34318876550133</v>
+        <v>10.22315991547686</v>
       </c>
       <c r="E55">
-        <v>14.98858</v>
+        <v>15.28244</v>
       </c>
       <c r="F55">
-        <v>15.57458</v>
+        <v>15.86844</v>
       </c>
       <c r="G55">
         <v>5.94</v>
@@ -5922,37 +5922,37 @@
         <v>1.4</v>
       </c>
       <c r="M55">
-        <v>3.672485964</v>
+        <v>3.741778152000001</v>
       </c>
       <c r="N55">
-        <v>-2.272485964</v>
+        <v>-2.341778152000001</v>
       </c>
       <c r="O55">
-        <v>-0.3863226138800001</v>
+        <v>-0.3981022858400001</v>
       </c>
       <c r="P55">
-        <v>-1.88616335012</v>
+        <v>-1.943675866160001</v>
       </c>
       <c r="Q55">
-        <v>-1.12616335012</v>
+        <v>-1.18367586616</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1930912496538764</v>
+        <v>0.1962932333420041</v>
       </c>
       <c r="T55">
-        <v>3.401645488542181</v>
+        <v>3.475594303510489</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.06480623815394383</v>
+        <v>0.06360612263257449</v>
       </c>
       <c r="W55">
-        <v>0.2205186890433</v>
+        <v>0.2208016762832389</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5960,7 +5960,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3812131656114343</v>
+        <v>0.3741536625445558</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5968,22 +5968,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2095277925302709</v>
+        <v>0.2114277925302709</v>
       </c>
       <c r="C56">
-        <v>0.2947199154768594</v>
+        <v>-0.1164151115138914</v>
       </c>
       <c r="D56">
-        <v>10.22315991547686</v>
+        <v>10.10588488848611</v>
       </c>
       <c r="E56">
-        <v>15.28244</v>
+        <v>15.5763</v>
       </c>
       <c r="F56">
-        <v>15.86844</v>
+        <v>16.1623</v>
       </c>
       <c r="G56">
         <v>5.94</v>
@@ -6004,37 +6004,37 @@
         <v>1.4</v>
       </c>
       <c r="M56">
-        <v>3.741778152000001</v>
+        <v>3.811070340000001</v>
       </c>
       <c r="N56">
-        <v>-2.341778152000001</v>
+        <v>-2.411070340000001</v>
       </c>
       <c r="O56">
-        <v>-0.3981022858400001</v>
+        <v>-0.4098819578000001</v>
       </c>
       <c r="P56">
-        <v>-1.943675866160001</v>
+        <v>-2.001188382200001</v>
       </c>
       <c r="Q56">
-        <v>-1.18367586616</v>
+        <v>-1.2411883822</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1962932333420041</v>
+        <v>0.1996375274162709</v>
       </c>
       <c r="T56">
-        <v>3.475594303510489</v>
+        <v>3.552829732477389</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.06360612263257449</v>
+        <v>0.06244964767561859</v>
       </c>
       <c r="W56">
-        <v>0.2208016762832389</v>
+        <v>0.2210743730780892</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -6042,7 +6042,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.3741536625445558</v>
+        <v>0.3673508686801094</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6050,22 +6050,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2114277925302709</v>
+        <v>0.213327792530271</v>
       </c>
       <c r="C57">
-        <v>-0.1164151115138914</v>
+        <v>-0.5248900121110829</v>
       </c>
       <c r="D57">
-        <v>10.10588488848611</v>
+        <v>9.991269987888918</v>
       </c>
       <c r="E57">
-        <v>15.5763</v>
+        <v>15.87016</v>
       </c>
       <c r="F57">
-        <v>16.1623</v>
+        <v>16.45616</v>
       </c>
       <c r="G57">
         <v>5.94</v>
@@ -6086,37 +6086,37 @@
         <v>1.4</v>
       </c>
       <c r="M57">
-        <v>3.811070340000001</v>
+        <v>3.880362528</v>
       </c>
       <c r="N57">
-        <v>-2.411070340000001</v>
+        <v>-2.480362528000001</v>
       </c>
       <c r="O57">
-        <v>-0.4098819578000001</v>
+        <v>-0.4216616297600001</v>
       </c>
       <c r="P57">
-        <v>-2.001188382200001</v>
+        <v>-2.058700898240001</v>
       </c>
       <c r="Q57">
-        <v>-1.2411883822</v>
+        <v>-1.29870089824</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1996375274162709</v>
+        <v>0.2031338348575498</v>
       </c>
       <c r="T57">
-        <v>3.552829732477389</v>
+        <v>3.633575862760966</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.06244964767561859</v>
+        <v>0.06133447539569684</v>
       </c>
       <c r="W57">
-        <v>0.2210743730780892</v>
+        <v>0.2213373307016947</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -6124,7 +6124,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3673508686801094</v>
+        <v>0.3607910317393931</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6132,22 +6132,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.213327792530271</v>
+        <v>0.2152277925302709</v>
       </c>
       <c r="C58">
-        <v>-0.5248900121110829</v>
+        <v>-0.9307942800171105</v>
       </c>
       <c r="D58">
-        <v>9.991269987888918</v>
+        <v>9.879225719982891</v>
       </c>
       <c r="E58">
-        <v>15.87016</v>
+        <v>16.16402</v>
       </c>
       <c r="F58">
-        <v>16.45616</v>
+        <v>16.75002</v>
       </c>
       <c r="G58">
         <v>5.94</v>
@@ -6168,37 +6168,37 @@
         <v>1.4</v>
       </c>
       <c r="M58">
-        <v>3.880362528</v>
+        <v>3.949654716000001</v>
       </c>
       <c r="N58">
-        <v>-2.480362528000001</v>
+        <v>-2.549654716000001</v>
       </c>
       <c r="O58">
-        <v>-0.4216616297600001</v>
+        <v>-0.4334413017200002</v>
       </c>
       <c r="P58">
-        <v>-2.058700898240001</v>
+        <v>-2.116213414280001</v>
       </c>
       <c r="Q58">
-        <v>-1.29870089824</v>
+        <v>-1.35621341428</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2031338348575498</v>
+        <v>0.2067927612495858</v>
       </c>
       <c r="T58">
-        <v>3.633575862760966</v>
+        <v>3.718077627011221</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.06133447539569684</v>
+        <v>0.06025843196770216</v>
       </c>
       <c r="W58">
-        <v>0.2213373307016947</v>
+        <v>0.2215910617420158</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3607910317393931</v>
+        <v>0.3544613645158949</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6214,22 +6214,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2152277925302709</v>
+        <v>0.217127792530271</v>
       </c>
       <c r="C59">
-        <v>-0.9307942800171105</v>
+        <v>-1.33421343904644</v>
       </c>
       <c r="D59">
-        <v>9.879225719982891</v>
+        <v>9.769666560953562</v>
       </c>
       <c r="E59">
-        <v>16.16402</v>
+        <v>16.45788</v>
       </c>
       <c r="F59">
-        <v>16.75002</v>
+        <v>17.04388</v>
       </c>
       <c r="G59">
         <v>5.94</v>
@@ -6250,37 +6250,37 @@
         <v>1.4</v>
       </c>
       <c r="M59">
-        <v>3.949654716000001</v>
+        <v>4.018946904000001</v>
       </c>
       <c r="N59">
-        <v>-2.549654716000001</v>
+        <v>-2.618946904000001</v>
       </c>
       <c r="O59">
-        <v>-0.4334413017200002</v>
+        <v>-0.4452209736800002</v>
       </c>
       <c r="P59">
-        <v>-2.116213414280001</v>
+        <v>-2.173725930320001</v>
       </c>
       <c r="Q59">
-        <v>-1.35621341428</v>
+        <v>-1.41372593032</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2067927612495858</v>
+        <v>0.2106259222317189</v>
       </c>
       <c r="T59">
-        <v>3.718077627011221</v>
+        <v>3.806603284797203</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.06025843196770216</v>
+        <v>0.05921949348550039</v>
       </c>
       <c r="W59">
-        <v>0.2215910617420158</v>
+        <v>0.221836043436119</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6288,7 +6288,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.3544613645158949</v>
+        <v>0.348349961679414</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6296,22 +6296,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2171277925302709</v>
+        <v>0.2190277925302709</v>
       </c>
       <c r="C60">
-        <v>-1.334213439046437</v>
+        <v>-1.73522926083853</v>
       </c>
       <c r="D60">
-        <v>9.769666560953562</v>
+        <v>9.662510739161471</v>
       </c>
       <c r="E60">
-        <v>16.45788</v>
+        <v>16.75174</v>
       </c>
       <c r="F60">
-        <v>17.04388</v>
+        <v>17.33774</v>
       </c>
       <c r="G60">
         <v>5.94</v>
@@ -6332,37 +6332,37 @@
         <v>1.4</v>
       </c>
       <c r="M60">
-        <v>4.018946904</v>
+        <v>4.088239092</v>
       </c>
       <c r="N60">
-        <v>-2.618946904</v>
+        <v>-2.688239092</v>
       </c>
       <c r="O60">
-        <v>-0.44522097368</v>
+        <v>-0.4570006456400001</v>
       </c>
       <c r="P60">
-        <v>-2.17372593032</v>
+        <v>-2.23123844636</v>
       </c>
       <c r="Q60">
-        <v>-1.41372593032</v>
+        <v>-1.47123844636</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2106259222317188</v>
+        <v>0.2146460666763949</v>
       </c>
       <c r="T60">
-        <v>3.806603284797201</v>
+        <v>3.899447267353231</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.0592194934855004</v>
+        <v>0.05821577325693259</v>
       </c>
       <c r="W60">
-        <v>0.221836043436119</v>
+        <v>0.2220727206660153</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6370,7 +6370,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3483499616794141</v>
+        <v>0.34244572504078</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6378,22 +6378,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2190277925302709</v>
+        <v>0.2209277925302709</v>
       </c>
       <c r="C61">
-        <v>-1.73522926083853</v>
+        <v>-2.133919968398747</v>
       </c>
       <c r="D61">
-        <v>9.662510739161471</v>
+        <v>9.557680031601253</v>
       </c>
       <c r="E61">
-        <v>16.75174</v>
+        <v>17.0456</v>
       </c>
       <c r="F61">
-        <v>17.33774</v>
+        <v>17.6316</v>
       </c>
       <c r="G61">
         <v>5.94</v>
@@ -6414,37 +6414,37 @@
         <v>1.4</v>
       </c>
       <c r="M61">
-        <v>4.088239092</v>
+        <v>4.15753128</v>
       </c>
       <c r="N61">
-        <v>-2.688239092</v>
+        <v>-2.75753128</v>
       </c>
       <c r="O61">
-        <v>-0.4570006456400001</v>
+        <v>-0.4687803176</v>
       </c>
       <c r="P61">
-        <v>-2.23123844636</v>
+        <v>-2.2887509624</v>
       </c>
       <c r="Q61">
-        <v>-1.47123844636</v>
+        <v>-1.5287509624</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2146460666763949</v>
+        <v>0.2188672183433047</v>
       </c>
       <c r="T61">
-        <v>3.899447267353231</v>
+        <v>3.996933449037062</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.05821577325693259</v>
+        <v>0.05724551036931706</v>
       </c>
       <c r="W61">
-        <v>0.2220727206660153</v>
+        <v>0.222301508654915</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.34244572504078</v>
+        <v>0.3367382962901003</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6460,22 +6460,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2209277925302709</v>
+        <v>0.222827792530271</v>
       </c>
       <c r="C62">
-        <v>-2.133919968398747</v>
+        <v>-2.530360426531821</v>
       </c>
       <c r="D62">
-        <v>9.557680031601253</v>
+        <v>9.455099573468175</v>
       </c>
       <c r="E62">
-        <v>17.0456</v>
+        <v>17.33946</v>
       </c>
       <c r="F62">
-        <v>17.6316</v>
+        <v>17.92546</v>
       </c>
       <c r="G62">
         <v>5.94</v>
@@ -6496,37 +6496,37 @@
         <v>1.4</v>
       </c>
       <c r="M62">
-        <v>4.15753128</v>
+        <v>4.226823467999999</v>
       </c>
       <c r="N62">
-        <v>-2.75753128</v>
+        <v>-2.826823467999999</v>
       </c>
       <c r="O62">
-        <v>-0.4687803176</v>
+        <v>-0.4805599895599999</v>
       </c>
       <c r="P62">
-        <v>-2.2887509624</v>
+        <v>-2.346263478439999</v>
       </c>
       <c r="Q62">
-        <v>-1.5287509624</v>
+        <v>-1.586263478439999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2188672183433047</v>
+        <v>0.2233048393264664</v>
       </c>
       <c r="T62">
-        <v>3.996933449037062</v>
+        <v>4.099418922089295</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.05724551036931706</v>
+        <v>0.05630705937965613</v>
       </c>
       <c r="W62">
-        <v>0.222301508654915</v>
+        <v>0.2225227953982771</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6534,7 +6534,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.3367382962901003</v>
+        <v>0.3312179963509184</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6542,22 +6542,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.222827792530271</v>
+        <v>0.2247277925302709</v>
       </c>
       <c r="C63">
-        <v>-2.530360426531821</v>
+        <v>-2.924622320142344</v>
       </c>
       <c r="D63">
-        <v>9.455099573468175</v>
+        <v>9.354697679857654</v>
       </c>
       <c r="E63">
-        <v>17.33946</v>
+        <v>17.63332</v>
       </c>
       <c r="F63">
-        <v>17.92546</v>
+        <v>18.21932</v>
       </c>
       <c r="G63">
         <v>5.94</v>
@@ -6578,37 +6578,37 @@
         <v>1.4</v>
       </c>
       <c r="M63">
-        <v>4.226823467999999</v>
+        <v>4.296115656</v>
       </c>
       <c r="N63">
-        <v>-2.826823467999999</v>
+        <v>-2.896115656000001</v>
       </c>
       <c r="O63">
-        <v>-0.4805599895599999</v>
+        <v>-0.4923396615200001</v>
       </c>
       <c r="P63">
-        <v>-2.346263478439999</v>
+        <v>-2.403775994480001</v>
       </c>
       <c r="Q63">
-        <v>-1.586263478439999</v>
+        <v>-1.64377599448</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2233048393264664</v>
+        <v>0.2279760193087419</v>
       </c>
       <c r="T63">
-        <v>4.099418922089295</v>
+        <v>4.207298367407434</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.05630705937965613</v>
+        <v>0.05539888100256489</v>
       </c>
       <c r="W63">
-        <v>0.2225227953982771</v>
+        <v>0.2227369438595952</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3312179963509184</v>
+        <v>0.3258757706033228</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6624,22 +6624,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2247277925302709</v>
+        <v>0.2266277925302709</v>
       </c>
       <c r="C64">
-        <v>-2.924622320142344</v>
+        <v>-3.31677432129451</v>
       </c>
       <c r="D64">
-        <v>9.354697679857654</v>
+        <v>9.256405678705487</v>
       </c>
       <c r="E64">
-        <v>17.63332</v>
+        <v>17.92718</v>
       </c>
       <c r="F64">
-        <v>18.21932</v>
+        <v>18.51318</v>
       </c>
       <c r="G64">
         <v>5.94</v>
@@ -6660,37 +6660,37 @@
         <v>1.4</v>
       </c>
       <c r="M64">
-        <v>4.296115656</v>
+        <v>4.365407844</v>
       </c>
       <c r="N64">
-        <v>-2.896115656000001</v>
+        <v>-2.965407844</v>
       </c>
       <c r="O64">
-        <v>-0.4923396615200001</v>
+        <v>-0.50411933348</v>
       </c>
       <c r="P64">
-        <v>-2.403775994480001</v>
+        <v>-2.46128851052</v>
       </c>
       <c r="Q64">
-        <v>-1.64377599448</v>
+        <v>-1.70128851052</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2279760193087419</v>
+        <v>0.2328996955062754</v>
       </c>
       <c r="T64">
-        <v>4.207298367407434</v>
+        <v>4.321009134094121</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.05539888100256489</v>
+        <v>0.05451953368506386</v>
       </c>
       <c r="W64">
-        <v>0.2227369438595952</v>
+        <v>0.2229442939570619</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6698,7 +6698,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.3258757706033228</v>
+        <v>0.320703139323905</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6706,22 +6706,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2266277925302709</v>
+        <v>0.2285277925302709</v>
       </c>
       <c r="C65">
-        <v>-3.31677432129451</v>
+        <v>-3.706882245849432</v>
       </c>
       <c r="D65">
-        <v>9.256405678705487</v>
+        <v>9.160157754150568</v>
       </c>
       <c r="E65">
-        <v>17.92718</v>
+        <v>18.22104</v>
       </c>
       <c r="F65">
-        <v>18.51318</v>
+        <v>18.80704</v>
       </c>
       <c r="G65">
         <v>5.94</v>
@@ -6742,37 +6742,37 @@
         <v>1.4</v>
       </c>
       <c r="M65">
-        <v>4.365407844</v>
+        <v>4.434700032</v>
       </c>
       <c r="N65">
-        <v>-2.965407844</v>
+        <v>-3.034700032</v>
       </c>
       <c r="O65">
-        <v>-0.50411933348</v>
+        <v>-0.5158990054400001</v>
       </c>
       <c r="P65">
-        <v>-2.46128851052</v>
+        <v>-2.51880102656</v>
       </c>
       <c r="Q65">
-        <v>-1.70128851052</v>
+        <v>-1.75880102656</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2328996955062754</v>
+        <v>0.2380969092703386</v>
       </c>
       <c r="T65">
-        <v>4.321009134094121</v>
+        <v>4.441037165596736</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.05451953368506386</v>
+        <v>0.05366766597123473</v>
       </c>
       <c r="W65">
-        <v>0.2229442939570619</v>
+        <v>0.2231451643639829</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.320703139323905</v>
+        <v>0.315692152771969</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6788,22 +6788,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2285277925302709</v>
+        <v>0.230427792530271</v>
       </c>
       <c r="C66">
-        <v>-3.706882245849432</v>
+        <v>-4.095009200430674</v>
       </c>
       <c r="D66">
-        <v>9.160157754150568</v>
+        <v>9.065890799569326</v>
       </c>
       <c r="E66">
-        <v>18.22104</v>
+        <v>18.5149</v>
       </c>
       <c r="F66">
-        <v>18.80704</v>
+        <v>19.1009</v>
       </c>
       <c r="G66">
         <v>5.94</v>
@@ -6824,37 +6824,37 @@
         <v>1.4</v>
       </c>
       <c r="M66">
-        <v>4.434700032</v>
+        <v>4.50399222</v>
       </c>
       <c r="N66">
-        <v>-3.034700032</v>
+        <v>-3.10399222</v>
       </c>
       <c r="O66">
-        <v>-0.5158990054400001</v>
+        <v>-0.5276786774</v>
       </c>
       <c r="P66">
-        <v>-2.51880102656</v>
+        <v>-2.5763135426</v>
       </c>
       <c r="Q66">
-        <v>-1.75880102656</v>
+        <v>-1.8163135426</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2380969092703386</v>
+        <v>0.2435911066780626</v>
       </c>
       <c r="T66">
-        <v>4.441037165596736</v>
+        <v>4.567923941756644</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.05366766597123473</v>
+        <v>0.05284200957167728</v>
       </c>
       <c r="W66">
-        <v>0.2231451643639829</v>
+        <v>0.2233398541429985</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6862,7 +6862,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.315692152771969</v>
+        <v>0.310835350421631</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6870,22 +6870,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.230427792530271</v>
+        <v>0.2323277925302709</v>
       </c>
       <c r="C67">
-        <v>-4.095009200430674</v>
+        <v>-4.481215720407778</v>
       </c>
       <c r="D67">
-        <v>9.065890799569326</v>
+        <v>8.973544279592222</v>
       </c>
       <c r="E67">
-        <v>18.5149</v>
+        <v>18.80876</v>
       </c>
       <c r="F67">
-        <v>19.1009</v>
+        <v>19.39476</v>
       </c>
       <c r="G67">
         <v>5.94</v>
@@ -6906,37 +6906,37 @@
         <v>1.4</v>
       </c>
       <c r="M67">
-        <v>4.50399222</v>
+        <v>4.573284408</v>
       </c>
       <c r="N67">
-        <v>-3.10399222</v>
+        <v>-3.173284408</v>
       </c>
       <c r="O67">
-        <v>-0.5276786774</v>
+        <v>-0.53945834936</v>
       </c>
       <c r="P67">
-        <v>-2.5763135426</v>
+        <v>-2.63382605864</v>
       </c>
       <c r="Q67">
-        <v>-1.8163135426</v>
+        <v>-1.87382605864</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2435911066780626</v>
+        <v>0.2494084921685939</v>
       </c>
       <c r="T67">
-        <v>4.567923941756644</v>
+        <v>4.702274645925956</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.05284200957167728</v>
+        <v>0.0520413730630155</v>
       </c>
       <c r="W67">
-        <v>0.2233398541429985</v>
+        <v>0.223528644231741</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6944,7 +6944,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.310835350421631</v>
+        <v>0.3061257239000912</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6952,22 +6952,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2323277925302709</v>
+        <v>0.2342277925302709</v>
       </c>
       <c r="C68">
-        <v>-4.481215720407778</v>
+        <v>-4.865559899531654</v>
       </c>
       <c r="D68">
-        <v>8.973544279592222</v>
+        <v>8.883060100468347</v>
       </c>
       <c r="E68">
-        <v>18.80876</v>
+        <v>19.10262</v>
       </c>
       <c r="F68">
-        <v>19.39476</v>
+        <v>19.68862</v>
       </c>
       <c r="G68">
         <v>5.94</v>
@@ -6988,37 +6988,37 @@
         <v>1.4</v>
       </c>
       <c r="M68">
-        <v>4.573284408</v>
+        <v>4.642576596</v>
       </c>
       <c r="N68">
-        <v>-3.173284408</v>
+        <v>-3.242576596000001</v>
       </c>
       <c r="O68">
-        <v>-0.53945834936</v>
+        <v>-0.5512380213200001</v>
       </c>
       <c r="P68">
-        <v>-2.63382605864</v>
+        <v>-2.69133857468</v>
       </c>
       <c r="Q68">
-        <v>-1.87382605864</v>
+        <v>-1.93133857468</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2494084921685939</v>
+        <v>0.2555784464767331</v>
       </c>
       <c r="T68">
-        <v>4.702274645925956</v>
+        <v>4.844767817014621</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.0520413730630155</v>
+        <v>0.05126463615162721</v>
       </c>
       <c r="W68">
-        <v>0.223528644231741</v>
+        <v>0.2237117987954463</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3061257239000912</v>
+        <v>0.301556683244866</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7034,22 +7034,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2342277925302709</v>
+        <v>0.2361277925302709</v>
       </c>
       <c r="C69">
-        <v>-4.865559899531654</v>
+        <v>-5.248097511805256</v>
       </c>
       <c r="D69">
-        <v>8.883060100468347</v>
+        <v>8.794382488194746</v>
       </c>
       <c r="E69">
-        <v>19.10262</v>
+        <v>19.39648</v>
       </c>
       <c r="F69">
-        <v>19.68862</v>
+        <v>19.98248</v>
       </c>
       <c r="G69">
         <v>5.94</v>
@@ -7070,37 +7070,37 @@
         <v>1.4</v>
       </c>
       <c r="M69">
-        <v>4.642576596</v>
+        <v>4.711868784000001</v>
       </c>
       <c r="N69">
-        <v>-3.242576596000001</v>
+        <v>-3.311868784000001</v>
       </c>
       <c r="O69">
-        <v>-0.5512380213200001</v>
+        <v>-0.5630176932800002</v>
       </c>
       <c r="P69">
-        <v>-2.69133857468</v>
+        <v>-2.748851090720001</v>
       </c>
       <c r="Q69">
-        <v>-1.93133857468</v>
+        <v>-1.98885109072</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2555784464767331</v>
+        <v>0.262134022929131</v>
       </c>
       <c r="T69">
-        <v>4.844767817014621</v>
+        <v>4.996166811296328</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.05126463615162721</v>
+        <v>0.05051074444351503</v>
       </c>
       <c r="W69">
-        <v>0.2237117987954463</v>
+        <v>0.2238895664602192</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7108,7 +7108,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.301556683244866</v>
+        <v>0.2971220261383237</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7116,22 +7116,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2361277925302709</v>
+        <v>0.238027792530271</v>
       </c>
       <c r="C70">
-        <v>-5.248097511805256</v>
+        <v>-5.628882126126772</v>
       </c>
       <c r="D70">
-        <v>8.794382488194746</v>
+        <v>8.70745787387323</v>
       </c>
       <c r="E70">
-        <v>19.39648</v>
+        <v>19.69034</v>
       </c>
       <c r="F70">
-        <v>19.98248</v>
+        <v>20.27634</v>
       </c>
       <c r="G70">
         <v>5.94</v>
@@ -7152,37 +7152,37 @@
         <v>1.4</v>
       </c>
       <c r="M70">
-        <v>4.711868784000001</v>
+        <v>4.781160972</v>
       </c>
       <c r="N70">
-        <v>-3.311868784000001</v>
+        <v>-3.381160972</v>
       </c>
       <c r="O70">
-        <v>-0.5630176932800002</v>
+        <v>-0.5747973652400001</v>
       </c>
       <c r="P70">
-        <v>-2.748851090720001</v>
+        <v>-2.80636360676</v>
       </c>
       <c r="Q70">
-        <v>-1.98885109072</v>
+        <v>-2.04636360676</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.262134022929131</v>
+        <v>0.2691125397978126</v>
       </c>
       <c r="T70">
-        <v>4.996166811296328</v>
+        <v>5.157333482628468</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.05051074444351503</v>
+        <v>0.04977870466897135</v>
       </c>
       <c r="W70">
-        <v>0.2238895664602192</v>
+        <v>0.2240621814390566</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2971220261383237</v>
+        <v>0.2928159098174785</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7198,22 +7198,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.238027792530271</v>
+        <v>0.239927792530271</v>
       </c>
       <c r="C71">
-        <v>-5.628882126126772</v>
+        <v>-6.007965214200464</v>
       </c>
       <c r="D71">
-        <v>8.70745787387323</v>
+        <v>8.622234785799536</v>
       </c>
       <c r="E71">
-        <v>19.69034</v>
+        <v>19.9842</v>
       </c>
       <c r="F71">
-        <v>20.27634</v>
+        <v>20.5702</v>
       </c>
       <c r="G71">
         <v>5.94</v>
@@ -7234,37 +7234,37 @@
         <v>1.4</v>
       </c>
       <c r="M71">
-        <v>4.781160972</v>
+        <v>4.85045316</v>
       </c>
       <c r="N71">
-        <v>-3.381160972</v>
+        <v>-3.45045316</v>
       </c>
       <c r="O71">
-        <v>-0.5747973652400001</v>
+        <v>-0.5865770372</v>
       </c>
       <c r="P71">
-        <v>-2.80636360676</v>
+        <v>-2.8638761228</v>
       </c>
       <c r="Q71">
-        <v>-2.04636360676</v>
+        <v>-2.1038761228</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2691125397978126</v>
+        <v>0.2765562911244064</v>
       </c>
       <c r="T71">
-        <v>5.157333482628468</v>
+        <v>5.329244598716084</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.04977870466897135</v>
+        <v>0.04906758031655747</v>
       </c>
       <c r="W71">
-        <v>0.2240621814390566</v>
+        <v>0.2242298645613558</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2928159098174785</v>
+        <v>0.2886328253915146</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7280,22 +7280,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.239927792530271</v>
+        <v>0.2418277925302709</v>
       </c>
       <c r="C72">
-        <v>-6.007965214200464</v>
+        <v>-6.385396252171976</v>
       </c>
       <c r="D72">
-        <v>8.622234785799536</v>
+        <v>8.538663747828025</v>
       </c>
       <c r="E72">
-        <v>19.9842</v>
+        <v>20.27806</v>
       </c>
       <c r="F72">
-        <v>20.5702</v>
+        <v>20.86406</v>
       </c>
       <c r="G72">
         <v>5.94</v>
@@ -7316,37 +7316,37 @@
         <v>1.4</v>
       </c>
       <c r="M72">
-        <v>4.85045316</v>
+        <v>4.919745348000001</v>
       </c>
       <c r="N72">
-        <v>-3.45045316</v>
+        <v>-3.519745348000001</v>
       </c>
       <c r="O72">
-        <v>-0.5865770372</v>
+        <v>-0.5983567091600003</v>
       </c>
       <c r="P72">
-        <v>-2.8638761228</v>
+        <v>-2.921388638840001</v>
       </c>
       <c r="Q72">
-        <v>-2.1038761228</v>
+        <v>-2.161388638840001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2765562911244064</v>
+        <v>0.2845134046114549</v>
       </c>
       <c r="T72">
-        <v>5.329244598716084</v>
+        <v>5.513011653844225</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.04906758031655747</v>
+        <v>0.04837648763604258</v>
       </c>
       <c r="W72">
-        <v>0.2242298645613558</v>
+        <v>0.2243928242154211</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.2886328253915146</v>
+        <v>0.2845675743296622</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7362,22 +7362,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2418277925302709</v>
+        <v>0.2437277925302709</v>
       </c>
       <c r="C73">
-        <v>-6.385396252171972</v>
+        <v>-6.761222816409745</v>
       </c>
       <c r="D73">
-        <v>8.538663747828025</v>
+        <v>8.456697183590251</v>
       </c>
       <c r="E73">
-        <v>20.27806</v>
+        <v>20.57192</v>
       </c>
       <c r="F73">
-        <v>20.86406</v>
+        <v>21.15792</v>
       </c>
       <c r="G73">
         <v>5.94</v>
@@ -7398,37 +7398,37 @@
         <v>1.4</v>
       </c>
       <c r="M73">
-        <v>4.919745348</v>
+        <v>4.989037536</v>
       </c>
       <c r="N73">
-        <v>-3.519745348</v>
+        <v>-3.589037536</v>
       </c>
       <c r="O73">
-        <v>-0.5983567091600001</v>
+        <v>-0.61013638112</v>
       </c>
       <c r="P73">
-        <v>-2.92138863884</v>
+        <v>-2.97890115488</v>
       </c>
       <c r="Q73">
-        <v>-2.16138863884</v>
+        <v>-2.21890115488</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2845134046114549</v>
+        <v>0.2930388833475782</v>
       </c>
       <c r="T73">
-        <v>5.513011653844224</v>
+        <v>5.709904927195803</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.04837648763604258</v>
+        <v>0.04770459197443088</v>
       </c>
       <c r="W73">
-        <v>0.2243928242154211</v>
+        <v>0.2245512572124292</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2845675743296622</v>
+        <v>0.2806152469084169</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7444,22 +7444,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2437277925302709</v>
+        <v>0.2456277925302709</v>
       </c>
       <c r="C74">
-        <v>-6.761222816409745</v>
+        <v>-7.135490673822211</v>
       </c>
       <c r="D74">
-        <v>8.456697183590251</v>
+        <v>8.376289326177787</v>
       </c>
       <c r="E74">
-        <v>20.57192</v>
+        <v>20.86578</v>
       </c>
       <c r="F74">
-        <v>21.15792</v>
+        <v>21.45178</v>
       </c>
       <c r="G74">
         <v>5.94</v>
@@ -7480,37 +7480,37 @@
         <v>1.4</v>
       </c>
       <c r="M74">
-        <v>4.989037536</v>
+        <v>5.058329724</v>
       </c>
       <c r="N74">
-        <v>-3.589037536</v>
+        <v>-3.658329724</v>
       </c>
       <c r="O74">
-        <v>-0.61013638112</v>
+        <v>-0.6219160530800001</v>
       </c>
       <c r="P74">
-        <v>-2.97890115488</v>
+        <v>-3.03641367092</v>
       </c>
       <c r="Q74">
-        <v>-2.21890115488</v>
+        <v>-2.27641367092</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2930388833475782</v>
+        <v>0.3021958790271181</v>
       </c>
       <c r="T74">
-        <v>5.709904927195803</v>
+        <v>5.921382887462314</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.04770459197443088</v>
+        <v>0.04705110441313731</v>
       </c>
       <c r="W74">
-        <v>0.2245512572124292</v>
+        <v>0.2247053495793822</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7518,7 +7518,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2806152469084169</v>
+        <v>0.2767712024302195</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7526,22 +7526,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2456277925302709</v>
+        <v>0.2475277925302709</v>
       </c>
       <c r="C75">
-        <v>-7.135490673822211</v>
+        <v>-7.508243867070977</v>
       </c>
       <c r="D75">
-        <v>8.376289326177787</v>
+        <v>8.297396132929022</v>
       </c>
       <c r="E75">
-        <v>20.86578</v>
+        <v>21.15964</v>
       </c>
       <c r="F75">
-        <v>21.45178</v>
+        <v>21.74564</v>
       </c>
       <c r="G75">
         <v>5.94</v>
@@ -7562,37 +7562,37 @@
         <v>1.4</v>
       </c>
       <c r="M75">
-        <v>5.058329724</v>
+        <v>5.127621912</v>
       </c>
       <c r="N75">
-        <v>-3.658329724</v>
+        <v>-3.727621912</v>
       </c>
       <c r="O75">
-        <v>-0.6219160530800001</v>
+        <v>-0.6336957250399999</v>
       </c>
       <c r="P75">
-        <v>-3.03641367092</v>
+        <v>-3.09392618696</v>
       </c>
       <c r="Q75">
-        <v>-2.27641367092</v>
+        <v>-2.333926186959999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3021958790271181</v>
+        <v>0.3120572589896996</v>
       </c>
       <c r="T75">
-        <v>5.921382887462314</v>
+        <v>6.149128383133941</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.04705110441313731</v>
+        <v>0.04641527867782464</v>
       </c>
       <c r="W75">
-        <v>0.2247053495793822</v>
+        <v>0.2248552772877689</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7600,7 +7600,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2767712024302195</v>
+        <v>0.2730310510460273</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7608,22 +7608,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2475277925302709</v>
+        <v>0.249427792530271</v>
       </c>
       <c r="C76">
-        <v>-7.508243867070977</v>
+        <v>-7.879524795013424</v>
       </c>
       <c r="D76">
-        <v>8.297396132929022</v>
+        <v>8.219975204986575</v>
       </c>
       <c r="E76">
-        <v>21.15964</v>
+        <v>21.4535</v>
       </c>
       <c r="F76">
-        <v>21.74564</v>
+        <v>22.0395</v>
       </c>
       <c r="G76">
         <v>5.94</v>
@@ -7644,37 +7644,37 @@
         <v>1.4</v>
       </c>
       <c r="M76">
-        <v>5.127621912</v>
+        <v>5.1969141</v>
       </c>
       <c r="N76">
-        <v>-3.727621912</v>
+        <v>-3.7969141</v>
       </c>
       <c r="O76">
-        <v>-0.6336957250399999</v>
+        <v>-0.645475397</v>
       </c>
       <c r="P76">
-        <v>-3.09392618696</v>
+        <v>-3.151438703</v>
       </c>
       <c r="Q76">
-        <v>-2.333926186959999</v>
+        <v>-2.391438703</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3120572589896996</v>
+        <v>0.3227075493492876</v>
       </c>
       <c r="T76">
-        <v>6.149128383133941</v>
+        <v>6.3950935184593</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.04641527867782464</v>
+        <v>0.04579640829545364</v>
       </c>
       <c r="W76">
-        <v>0.2248552772877689</v>
+        <v>0.2250012069239321</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2730310510460273</v>
+        <v>0.2693906370320802</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7690,22 +7690,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.249427792530271</v>
+        <v>0.2513277925302709</v>
       </c>
       <c r="C77">
-        <v>-7.879524795013424</v>
+        <v>-8.249374288683356</v>
       </c>
       <c r="D77">
-        <v>8.219975204986575</v>
+        <v>8.143985711316644</v>
       </c>
       <c r="E77">
-        <v>21.4535</v>
+        <v>21.74736</v>
       </c>
       <c r="F77">
-        <v>22.0395</v>
+        <v>22.33336</v>
       </c>
       <c r="G77">
         <v>5.94</v>
@@ -7726,37 +7726,37 @@
         <v>1.4</v>
       </c>
       <c r="M77">
-        <v>5.1969141</v>
+        <v>5.266206288</v>
       </c>
       <c r="N77">
-        <v>-3.7969141</v>
+        <v>-3.866206288</v>
       </c>
       <c r="O77">
-        <v>-0.645475397</v>
+        <v>-0.6572550689600001</v>
       </c>
       <c r="P77">
-        <v>-3.151438703</v>
+        <v>-3.20895121904</v>
       </c>
       <c r="Q77">
-        <v>-2.391438703</v>
+        <v>-2.44895121904</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3227075493492876</v>
+        <v>0.334245363905508</v>
       </c>
       <c r="T77">
-        <v>6.3950935184593</v>
+        <v>6.661555748395105</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.04579640829545364</v>
+        <v>0.04519382397577662</v>
       </c>
       <c r="W77">
-        <v>0.2250012069239321</v>
+        <v>0.2251432963065119</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7764,7 +7764,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2693906370320802</v>
+        <v>0.2658460233869213</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7772,22 +7772,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2513277925302709</v>
+        <v>0.2532277925302709</v>
       </c>
       <c r="C78">
-        <v>-8.249374288683356</v>
+        <v>-8.617831683095893</v>
       </c>
       <c r="D78">
-        <v>8.143985711316644</v>
+        <v>8.069388316904108</v>
       </c>
       <c r="E78">
-        <v>21.74736</v>
+        <v>22.04122</v>
       </c>
       <c r="F78">
-        <v>22.33336</v>
+        <v>22.62722</v>
       </c>
       <c r="G78">
         <v>5.94</v>
@@ -7808,37 +7808,37 @@
         <v>1.4</v>
       </c>
       <c r="M78">
-        <v>5.266206288</v>
+        <v>5.335498476000001</v>
       </c>
       <c r="N78">
-        <v>-3.866206288</v>
+        <v>-3.935498476000001</v>
       </c>
       <c r="O78">
-        <v>-0.6572550689600001</v>
+        <v>-0.6690347409200001</v>
       </c>
       <c r="P78">
-        <v>-3.20895121904</v>
+        <v>-3.26646373508</v>
       </c>
       <c r="Q78">
-        <v>-2.44895121904</v>
+        <v>-2.50646373508</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.334245363905508</v>
+        <v>0.3467864666840083</v>
       </c>
       <c r="T78">
-        <v>6.661555748395105</v>
+        <v>6.951188607020978</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.04519382397577662</v>
+        <v>0.04460689119687043</v>
       </c>
       <c r="W78">
-        <v>0.2251432963065119</v>
+        <v>0.225281695055778</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2658460233869213</v>
+        <v>0.2623934776286495</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7854,22 +7854,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2532277925302709</v>
+        <v>0.255127792530271</v>
       </c>
       <c r="C79">
-        <v>-8.617831683095893</v>
+        <v>-8.984934885141794</v>
       </c>
       <c r="D79">
-        <v>8.069388316904108</v>
+        <v>7.996145114858205</v>
       </c>
       <c r="E79">
-        <v>22.04122</v>
+        <v>22.33508</v>
       </c>
       <c r="F79">
-        <v>22.62722</v>
+        <v>22.92108</v>
       </c>
       <c r="G79">
         <v>5.94</v>
@@ -7890,37 +7890,37 @@
         <v>1.4</v>
       </c>
       <c r="M79">
-        <v>5.335498476000001</v>
+        <v>5.404790664</v>
       </c>
       <c r="N79">
-        <v>-3.935498476000001</v>
+        <v>-4.004790664</v>
       </c>
       <c r="O79">
-        <v>-0.6690347409200001</v>
+        <v>-0.68081441288</v>
       </c>
       <c r="P79">
-        <v>-3.26646373508</v>
+        <v>-3.32397625112</v>
       </c>
       <c r="Q79">
-        <v>-2.50646373508</v>
+        <v>-2.563976251119999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3467864666840083</v>
+        <v>0.3604676697150996</v>
       </c>
       <c r="T79">
-        <v>6.951188607020978</v>
+        <v>7.267151725521932</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.04460689119687043</v>
+        <v>0.04403500797639773</v>
       </c>
       <c r="W79">
-        <v>0.225281695055778</v>
+        <v>0.2254165451191654</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7928,7 +7928,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.2623934776286495</v>
+        <v>0.2590294586846926</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7936,22 +7936,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.255127792530271</v>
+        <v>0.257027792530271</v>
       </c>
       <c r="C80">
-        <v>-8.984934885141794</v>
+        <v>-9.350720437817607</v>
       </c>
       <c r="D80">
-        <v>7.996145114858205</v>
+        <v>7.924219562182396</v>
       </c>
       <c r="E80">
-        <v>22.33508</v>
+        <v>22.62894</v>
       </c>
       <c r="F80">
-        <v>22.92108</v>
+        <v>23.21494</v>
       </c>
       <c r="G80">
         <v>5.94</v>
@@ -7972,37 +7972,37 @@
         <v>1.4</v>
       </c>
       <c r="M80">
-        <v>5.404790664</v>
+        <v>5.474082852</v>
       </c>
       <c r="N80">
-        <v>-4.004790664</v>
+        <v>-4.074082852</v>
       </c>
       <c r="O80">
-        <v>-0.68081441288</v>
+        <v>-0.6925940848400001</v>
       </c>
       <c r="P80">
-        <v>-3.32397625112</v>
+        <v>-3.38148876716</v>
       </c>
       <c r="Q80">
-        <v>-2.563976251119999</v>
+        <v>-2.62148876716</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3604676697150996</v>
+        <v>0.3754518444634377</v>
       </c>
       <c r="T80">
-        <v>7.267151725521932</v>
+        <v>7.613206569594406</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.04403500797639773</v>
+        <v>0.04347760281213953</v>
       </c>
       <c r="W80">
-        <v>0.2254165451191654</v>
+        <v>0.2255479812568975</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2590294586846926</v>
+        <v>0.2557506047772914</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8018,22 +8018,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.257027792530271</v>
+        <v>0.258927792530271</v>
       </c>
       <c r="C81">
-        <v>-9.350720437817607</v>
+        <v>-9.715223581020094</v>
       </c>
       <c r="D81">
-        <v>7.924219562182396</v>
+        <v>7.853576418979905</v>
       </c>
       <c r="E81">
-        <v>22.62894</v>
+        <v>22.9228</v>
       </c>
       <c r="F81">
-        <v>23.21494</v>
+        <v>23.5088</v>
       </c>
       <c r="G81">
         <v>5.94</v>
@@ -8054,37 +8054,37 @@
         <v>1.4</v>
       </c>
       <c r="M81">
-        <v>5.474082852</v>
+        <v>5.543375040000001</v>
       </c>
       <c r="N81">
-        <v>-4.074082852</v>
+        <v>-4.14337504</v>
       </c>
       <c r="O81">
-        <v>-0.6925940848400001</v>
+        <v>-0.7043737568000001</v>
       </c>
       <c r="P81">
-        <v>-3.38148876716</v>
+        <v>-3.439001283200001</v>
       </c>
       <c r="Q81">
-        <v>-2.62148876716</v>
+        <v>-2.6790012832</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3754518444634377</v>
+        <v>0.3919344366866096</v>
       </c>
       <c r="T81">
-        <v>7.613206569594406</v>
+        <v>7.993866898074127</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.04347760281213953</v>
+        <v>0.04293413277698778</v>
       </c>
       <c r="W81">
-        <v>0.2255479812568975</v>
+        <v>0.2256761314911863</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2557506047772914</v>
+        <v>0.2525537222175752</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8100,22 +8100,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.258927792530271</v>
+        <v>0.2608277925302709</v>
       </c>
       <c r="C82">
-        <v>-9.715223581020094</v>
+        <v>-10.07847830911767</v>
       </c>
       <c r="D82">
-        <v>7.853576418979905</v>
+        <v>7.784181690882324</v>
       </c>
       <c r="E82">
-        <v>22.9228</v>
+        <v>23.21666</v>
       </c>
       <c r="F82">
-        <v>23.5088</v>
+        <v>23.80266</v>
       </c>
       <c r="G82">
         <v>5.94</v>
@@ -8136,37 +8136,37 @@
         <v>1.4</v>
       </c>
       <c r="M82">
-        <v>5.543375040000001</v>
+        <v>5.612667228</v>
       </c>
       <c r="N82">
-        <v>-4.14337504</v>
+        <v>-4.212667228000001</v>
       </c>
       <c r="O82">
-        <v>-0.7043737568000001</v>
+        <v>-0.7161534287600002</v>
       </c>
       <c r="P82">
-        <v>-3.439001283200001</v>
+        <v>-3.496513799240001</v>
       </c>
       <c r="Q82">
-        <v>-2.6790012832</v>
+        <v>-2.73651379924</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3919344366866096</v>
+        <v>0.4101520386174838</v>
       </c>
       <c r="T82">
-        <v>7.993866898074127</v>
+        <v>8.41459673481487</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.04293413277698778</v>
+        <v>0.04240408175504966</v>
       </c>
       <c r="W82">
-        <v>0.2256761314911863</v>
+        <v>0.2258011175221593</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.2525537222175752</v>
+        <v>0.2494357750297038</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8182,22 +8182,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2608277925302709</v>
+        <v>0.262727792530271</v>
       </c>
       <c r="C83">
-        <v>-10.07847830911767</v>
+        <v>-10.44051742549629</v>
       </c>
       <c r="D83">
-        <v>7.784181690882324</v>
+        <v>7.716002574503713</v>
       </c>
       <c r="E83">
-        <v>23.21666</v>
+        <v>23.51052</v>
       </c>
       <c r="F83">
-        <v>23.80266</v>
+        <v>24.09652</v>
       </c>
       <c r="G83">
         <v>5.94</v>
@@ -8218,37 +8218,37 @@
         <v>1.4</v>
       </c>
       <c r="M83">
-        <v>5.612667228</v>
+        <v>5.681959416000001</v>
       </c>
       <c r="N83">
-        <v>-4.212667228000001</v>
+        <v>-4.281959416000001</v>
       </c>
       <c r="O83">
-        <v>-0.7161534287600002</v>
+        <v>-0.7279331007200003</v>
       </c>
       <c r="P83">
-        <v>-3.496513799240001</v>
+        <v>-3.554026315280001</v>
       </c>
       <c r="Q83">
-        <v>-2.73651379924</v>
+        <v>-2.79402631528</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4101520386174838</v>
+        <v>0.4303938185406773</v>
       </c>
       <c r="T83">
-        <v>8.41459673481487</v>
+        <v>8.882074331193474</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.04240408175504966</v>
+        <v>0.04188695880681735</v>
       </c>
       <c r="W83">
-        <v>0.2258011175221593</v>
+        <v>0.2259230551133525</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2494357750297038</v>
+        <v>0.2463938753342196</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8264,22 +8264,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.262727792530271</v>
+        <v>0.2646277925302709</v>
       </c>
       <c r="C84">
-        <v>-10.44051742549629</v>
+        <v>-10.80137259426366</v>
       </c>
       <c r="D84">
-        <v>7.716002574503713</v>
+        <v>7.649007405736342</v>
       </c>
       <c r="E84">
-        <v>23.51052</v>
+        <v>23.80438</v>
       </c>
       <c r="F84">
-        <v>24.09652</v>
+        <v>24.39038</v>
       </c>
       <c r="G84">
         <v>5.94</v>
@@ -8300,37 +8300,37 @@
         <v>1.4</v>
       </c>
       <c r="M84">
-        <v>5.681959416000001</v>
+        <v>5.751251604</v>
       </c>
       <c r="N84">
-        <v>-4.281959416000001</v>
+        <v>-4.351251604</v>
       </c>
       <c r="O84">
-        <v>-0.7279331007200003</v>
+        <v>-0.73971277268</v>
       </c>
       <c r="P84">
-        <v>-3.554026315280001</v>
+        <v>-3.61153883132</v>
       </c>
       <c r="Q84">
-        <v>-2.79402631528</v>
+        <v>-2.85153883132</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4303938185406773</v>
+        <v>0.4530169843371878</v>
       </c>
       <c r="T84">
-        <v>8.882074331193474</v>
+        <v>9.404549291851914</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.04188695880681735</v>
+        <v>0.04138229665251835</v>
       </c>
       <c r="W84">
-        <v>0.2259230551133525</v>
+        <v>0.2260420544493362</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2463938753342196</v>
+        <v>0.2434252744265786</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8346,22 +8346,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2646277925302709</v>
+        <v>0.2665277925302709</v>
       </c>
       <c r="C85">
-        <v>-10.80137259426366</v>
+        <v>-11.16107438928323</v>
       </c>
       <c r="D85">
-        <v>7.649007405736342</v>
+        <v>7.583165610716777</v>
       </c>
       <c r="E85">
-        <v>23.80438</v>
+        <v>24.09824</v>
       </c>
       <c r="F85">
-        <v>24.39038</v>
+        <v>24.68424</v>
       </c>
       <c r="G85">
         <v>5.94</v>
@@ -8382,37 +8382,37 @@
         <v>1.4</v>
       </c>
       <c r="M85">
-        <v>5.751251604</v>
+        <v>5.820543792</v>
       </c>
       <c r="N85">
-        <v>-4.351251604</v>
+        <v>-4.420543792</v>
       </c>
       <c r="O85">
-        <v>-0.73971277268</v>
+        <v>-0.7514924446400001</v>
       </c>
       <c r="P85">
-        <v>-3.61153883132</v>
+        <v>-3.66905134736</v>
       </c>
       <c r="Q85">
-        <v>-2.85153883132</v>
+        <v>-2.90905134736</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4530169843371878</v>
+        <v>0.4784680458582622</v>
       </c>
       <c r="T85">
-        <v>9.404549291851914</v>
+        <v>9.992333622592662</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.04138229665251835</v>
+        <v>0.04088965026379789</v>
       </c>
       <c r="W85">
-        <v>0.2260420544493362</v>
+        <v>0.2261582204677965</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2434252744265786</v>
+        <v>0.2405273544929288</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8428,22 +8428,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2665277925302709</v>
+        <v>0.2684277925302709</v>
       </c>
       <c r="C86">
-        <v>-11.16107438928322</v>
+        <v>-11.51965234069714</v>
       </c>
       <c r="D86">
-        <v>7.583165610716777</v>
+        <v>7.518447659302858</v>
       </c>
       <c r="E86">
-        <v>24.09824</v>
+        <v>24.3921</v>
       </c>
       <c r="F86">
-        <v>24.68424</v>
+        <v>24.9781</v>
       </c>
       <c r="G86">
         <v>5.94</v>
@@ -8464,37 +8464,37 @@
         <v>1.4</v>
       </c>
       <c r="M86">
-        <v>5.820543792</v>
+        <v>5.88983598</v>
       </c>
       <c r="N86">
-        <v>-4.420543792</v>
+        <v>-4.489835980000001</v>
       </c>
       <c r="O86">
-        <v>-0.7514924446400001</v>
+        <v>-0.7632721166000002</v>
       </c>
       <c r="P86">
-        <v>-3.66905134736</v>
+        <v>-3.7265638634</v>
       </c>
       <c r="Q86">
-        <v>-2.90905134736</v>
+        <v>-2.9665638634</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4784680458582618</v>
+        <v>0.5073125822488127</v>
       </c>
       <c r="T86">
-        <v>9.992333622592653</v>
+        <v>10.65848919743217</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.0408896502637979</v>
+        <v>0.04040859555481204</v>
       </c>
       <c r="W86">
-        <v>0.2261582204677965</v>
+        <v>0.2262716531681753</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8502,7 +8502,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2405273544929287</v>
+        <v>0.2376976209106589</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8510,22 +8510,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2684277925302709</v>
+        <v>0.2703277925302709</v>
       </c>
       <c r="C87">
-        <v>-11.51965234069714</v>
+        <v>-11.87713497908721</v>
       </c>
       <c r="D87">
-        <v>7.518447659302858</v>
+        <v>7.454825020912785</v>
       </c>
       <c r="E87">
-        <v>24.3921</v>
+        <v>24.68596</v>
       </c>
       <c r="F87">
-        <v>24.9781</v>
+        <v>25.27196</v>
       </c>
       <c r="G87">
         <v>5.94</v>
@@ -8546,37 +8546,37 @@
         <v>1.4</v>
       </c>
       <c r="M87">
-        <v>5.88983598</v>
+        <v>5.959128168</v>
       </c>
       <c r="N87">
-        <v>-4.489835980000001</v>
+        <v>-4.559128168000001</v>
       </c>
       <c r="O87">
-        <v>-0.7632721166000002</v>
+        <v>-0.7750517885600002</v>
       </c>
       <c r="P87">
-        <v>-3.7265638634</v>
+        <v>-3.784076379440001</v>
       </c>
       <c r="Q87">
-        <v>-2.9665638634</v>
+        <v>-3.02407637944</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5073125822488127</v>
+        <v>0.5402777666951564</v>
       </c>
       <c r="T87">
-        <v>10.65848919743217</v>
+        <v>11.41980985439161</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.04040859555481204</v>
+        <v>0.0399387281646398</v>
       </c>
       <c r="W87">
-        <v>0.2262716531681753</v>
+        <v>0.2263824478987779</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8584,7 +8584,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2376976209106589</v>
+        <v>0.2349336950861164</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8592,22 +8592,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2703277925302709</v>
+        <v>0.2722277925302709</v>
       </c>
       <c r="C88">
-        <v>-11.87713497908721</v>
+        <v>-12.23354987741243</v>
       </c>
       <c r="D88">
-        <v>7.454825020912785</v>
+        <v>7.392270122587568</v>
       </c>
       <c r="E88">
-        <v>24.68596</v>
+        <v>24.97982</v>
       </c>
       <c r="F88">
-        <v>25.27196</v>
+        <v>25.56582</v>
       </c>
       <c r="G88">
         <v>5.94</v>
@@ -8628,37 +8628,37 @@
         <v>1.4</v>
       </c>
       <c r="M88">
-        <v>5.959128168</v>
+        <v>6.028420356</v>
       </c>
       <c r="N88">
-        <v>-4.559128168000001</v>
+        <v>-4.628420355999999</v>
       </c>
       <c r="O88">
-        <v>-0.7750517885600002</v>
+        <v>-0.78683146052</v>
       </c>
       <c r="P88">
-        <v>-3.784076379440001</v>
+        <v>-3.841588895479999</v>
       </c>
       <c r="Q88">
-        <v>-3.02407637944</v>
+        <v>-3.081588895479999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5402777666951564</v>
+        <v>0.5783145179793991</v>
       </c>
       <c r="T88">
-        <v>11.41980985439161</v>
+        <v>12.29825676626788</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.0399387281646398</v>
+        <v>0.03947966232366693</v>
       </c>
       <c r="W88">
-        <v>0.2263824478987779</v>
+        <v>0.2264906956240793</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2349336950861164</v>
+        <v>0.2322333077862762</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8674,22 +8674,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2722277925302709</v>
+        <v>0.2741277925302709</v>
       </c>
       <c r="C89">
-        <v>-12.23354987741243</v>
+        <v>-12.58892369085262</v>
       </c>
       <c r="D89">
-        <v>7.392270122587568</v>
+        <v>7.330756309147382</v>
       </c>
       <c r="E89">
-        <v>24.97982</v>
+        <v>25.27368</v>
       </c>
       <c r="F89">
-        <v>25.56582</v>
+        <v>25.85968</v>
       </c>
       <c r="G89">
         <v>5.94</v>
@@ -8710,37 +8710,37 @@
         <v>1.4</v>
       </c>
       <c r="M89">
-        <v>6.028420356</v>
+        <v>6.097712544</v>
       </c>
       <c r="N89">
-        <v>-4.628420355999999</v>
+        <v>-4.697712544</v>
       </c>
       <c r="O89">
-        <v>-0.78683146052</v>
+        <v>-0.79861113248</v>
       </c>
       <c r="P89">
-        <v>-3.841588895479999</v>
+        <v>-3.89910141152</v>
       </c>
       <c r="Q89">
-        <v>-3.081588895479999</v>
+        <v>-3.13910141152</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5783145179793991</v>
+        <v>0.6226907278110159</v>
       </c>
       <c r="T89">
-        <v>12.29825676626788</v>
+        <v>13.32311149679021</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.03947966232366693</v>
+        <v>0.03903102979726163</v>
       </c>
       <c r="W89">
-        <v>0.2264906956240793</v>
+        <v>0.2265964831738057</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8748,7 +8748,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2322333077862762</v>
+        <v>0.2295942929250685</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8756,22 +8756,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2741277925302709</v>
+        <v>0.2760277925302709</v>
       </c>
       <c r="C90">
-        <v>-12.58892369085262</v>
+        <v>-12.94328219467921</v>
       </c>
       <c r="D90">
-        <v>7.330756309147382</v>
+        <v>7.27025780532079</v>
       </c>
       <c r="E90">
-        <v>25.27368</v>
+        <v>25.56754</v>
       </c>
       <c r="F90">
-        <v>25.85968</v>
+        <v>26.15354</v>
       </c>
       <c r="G90">
         <v>5.94</v>
@@ -8792,37 +8792,37 @@
         <v>1.4</v>
       </c>
       <c r="M90">
-        <v>6.097712544</v>
+        <v>6.167004732000001</v>
       </c>
       <c r="N90">
-        <v>-4.697712544</v>
+        <v>-4.767004732</v>
       </c>
       <c r="O90">
-        <v>-0.79861113248</v>
+        <v>-0.8103908044400001</v>
       </c>
       <c r="P90">
-        <v>-3.89910141152</v>
+        <v>-3.95661392756</v>
       </c>
       <c r="Q90">
-        <v>-3.13910141152</v>
+        <v>-3.19661392756</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6226907278110159</v>
+        <v>0.675135339430199</v>
       </c>
       <c r="T90">
-        <v>13.32311149679021</v>
+        <v>14.53430345104386</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.03903102979726163</v>
+        <v>0.03859247890066318</v>
       </c>
       <c r="W90">
-        <v>0.2265964831738057</v>
+        <v>0.2266998934752236</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8830,7 +8830,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2295942929250685</v>
+        <v>0.227014581768607</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8838,22 +8838,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2760277925302709</v>
+        <v>0.2779277925302709</v>
       </c>
       <c r="C91">
-        <v>-12.94328219467921</v>
+        <v>-13.29665032026614</v>
       </c>
       <c r="D91">
-        <v>7.27025780532079</v>
+        <v>7.210749679733855</v>
       </c>
       <c r="E91">
-        <v>25.56754</v>
+        <v>25.8614</v>
       </c>
       <c r="F91">
-        <v>26.15354</v>
+        <v>26.4474</v>
       </c>
       <c r="G91">
         <v>5.94</v>
@@ -8874,37 +8874,37 @@
         <v>1.4</v>
       </c>
       <c r="M91">
-        <v>6.167004732000001</v>
+        <v>6.23629692</v>
       </c>
       <c r="N91">
-        <v>-4.767004732</v>
+        <v>-4.836296920000001</v>
       </c>
       <c r="O91">
-        <v>-0.8103908044400001</v>
+        <v>-0.8221704764000002</v>
       </c>
       <c r="P91">
-        <v>-3.95661392756</v>
+        <v>-4.0141264436</v>
       </c>
       <c r="Q91">
-        <v>-3.19661392756</v>
+        <v>-3.2541264436</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.675135339430199</v>
+        <v>0.738068873373219</v>
       </c>
       <c r="T91">
-        <v>14.53430345104386</v>
+        <v>15.98773379614825</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.03859247890066318</v>
+        <v>0.0381636735795447</v>
       </c>
       <c r="W91">
-        <v>0.2266998934752236</v>
+        <v>0.2268010057699434</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8912,7 +8912,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.227014581768607</v>
+        <v>0.2244921975267334</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8920,22 +8920,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2779277925302709</v>
+        <v>0.279827792530271</v>
       </c>
       <c r="C92">
-        <v>-13.29665032026614</v>
+        <v>-13.6490521893466</v>
       </c>
       <c r="D92">
-        <v>7.210749679733855</v>
+        <v>7.152207810653403</v>
       </c>
       <c r="E92">
-        <v>25.8614</v>
+        <v>26.15526</v>
       </c>
       <c r="F92">
-        <v>26.4474</v>
+        <v>26.74126</v>
       </c>
       <c r="G92">
         <v>5.94</v>
@@ -8956,37 +8956,37 @@
         <v>1.4</v>
       </c>
       <c r="M92">
-        <v>6.23629692</v>
+        <v>6.305589108</v>
       </c>
       <c r="N92">
-        <v>-4.836296920000001</v>
+        <v>-4.905589108000001</v>
       </c>
       <c r="O92">
-        <v>-0.8221704764000002</v>
+        <v>-0.8339501483600003</v>
       </c>
       <c r="P92">
-        <v>-4.0141264436</v>
+        <v>-4.07163895964</v>
       </c>
       <c r="Q92">
-        <v>-3.2541264436</v>
+        <v>-3.31163895964</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.738068873373219</v>
+        <v>0.8149876370813548</v>
       </c>
       <c r="T92">
-        <v>15.98773379614825</v>
+        <v>17.76414866238695</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.0381636735795447</v>
+        <v>0.03774429255119806</v>
       </c>
       <c r="W92">
-        <v>0.2268010057699434</v>
+        <v>0.2268998958164275</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2244921975267334</v>
+        <v>0.2220252503011649</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9002,22 +9002,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.279827792530271</v>
+        <v>0.281727792530271</v>
       </c>
       <c r="C93">
-        <v>-13.6490521893466</v>
+        <v>-14.00051114661441</v>
       </c>
       <c r="D93">
-        <v>7.152207810653403</v>
+        <v>7.094608853385584</v>
       </c>
       <c r="E93">
-        <v>26.15526</v>
+        <v>26.44912</v>
       </c>
       <c r="F93">
-        <v>26.74126</v>
+        <v>27.03512</v>
       </c>
       <c r="G93">
         <v>5.94</v>
@@ -9038,37 +9038,37 @@
         <v>1.4</v>
       </c>
       <c r="M93">
-        <v>6.305589108</v>
+        <v>6.374881296</v>
       </c>
       <c r="N93">
-        <v>-4.905589108000001</v>
+        <v>-4.974881296</v>
       </c>
       <c r="O93">
-        <v>-0.8339501483600003</v>
+        <v>-0.84572982032</v>
       </c>
       <c r="P93">
-        <v>-4.07163895964</v>
+        <v>-4.12915147568</v>
       </c>
       <c r="Q93">
-        <v>-3.31163895964</v>
+        <v>-3.369151475679999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8149876370813548</v>
+        <v>0.9111360917165243</v>
       </c>
       <c r="T93">
-        <v>17.76414866238695</v>
+        <v>19.98466724518532</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.03774429255119806</v>
+        <v>0.03733402850172851</v>
       </c>
       <c r="W93">
-        <v>0.2268998958164275</v>
+        <v>0.2269966360792924</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2220252503011649</v>
+        <v>0.2196119323631089</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9084,22 +9084,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.281727792530271</v>
+        <v>0.2836277925302709</v>
       </c>
       <c r="C94">
-        <v>-14.00051114661441</v>
+        <v>-14.35104979076286</v>
       </c>
       <c r="D94">
-        <v>7.094608853385584</v>
+        <v>7.037930209237145</v>
       </c>
       <c r="E94">
-        <v>26.44912</v>
+        <v>26.74298</v>
       </c>
       <c r="F94">
-        <v>27.03512</v>
+        <v>27.32898</v>
       </c>
       <c r="G94">
         <v>5.94</v>
@@ -9120,37 +9120,37 @@
         <v>1.4</v>
       </c>
       <c r="M94">
-        <v>6.374881296</v>
+        <v>6.444173484</v>
       </c>
       <c r="N94">
-        <v>-4.974881296</v>
+        <v>-5.044173484</v>
       </c>
       <c r="O94">
-        <v>-0.84572982032</v>
+        <v>-0.8575094922800001</v>
       </c>
       <c r="P94">
-        <v>-4.12915147568</v>
+        <v>-4.18666399172</v>
       </c>
       <c r="Q94">
-        <v>-3.369151475679999</v>
+        <v>-3.426663991719999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9111360917165243</v>
+        <v>1.034755533390314</v>
       </c>
       <c r="T94">
-        <v>19.98466724518532</v>
+        <v>22.83961970878323</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.03733402850172851</v>
+        <v>0.03693258733504326</v>
       </c>
       <c r="W94">
-        <v>0.2269966360792924</v>
+        <v>0.2270912959063968</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2196119323631089</v>
+        <v>0.2172505137355486</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9166,22 +9166,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2836277925302709</v>
+        <v>0.2855277925302709</v>
       </c>
       <c r="C95">
-        <v>-14.35104979076286</v>
+        <v>-14.70069000404731</v>
       </c>
       <c r="D95">
-        <v>7.037930209237145</v>
+        <v>6.982149995952687</v>
       </c>
       <c r="E95">
-        <v>26.74298</v>
+        <v>27.03684</v>
       </c>
       <c r="F95">
-        <v>27.32898</v>
+        <v>27.62284</v>
       </c>
       <c r="G95">
         <v>5.94</v>
@@ -9202,37 +9202,37 @@
         <v>1.4</v>
       </c>
       <c r="M95">
-        <v>6.444173484</v>
+        <v>6.513465672000001</v>
       </c>
       <c r="N95">
-        <v>-5.044173484</v>
+        <v>-5.113465672</v>
       </c>
       <c r="O95">
-        <v>-0.8575094922800001</v>
+        <v>-0.8692891642400001</v>
       </c>
       <c r="P95">
-        <v>-4.18666399172</v>
+        <v>-4.24417650776</v>
       </c>
       <c r="Q95">
-        <v>-3.426663991719999</v>
+        <v>-3.48417650776</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.034755533390314</v>
+        <v>1.199581455622033</v>
       </c>
       <c r="T95">
-        <v>22.83961970878323</v>
+        <v>26.64622299358044</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.03693258733504326</v>
+        <v>0.03653968746977684</v>
       </c>
       <c r="W95">
-        <v>0.2270912959063968</v>
+        <v>0.2271839416946266</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9240,7 +9240,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2172505137355486</v>
+        <v>0.2149393380575109</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9248,22 +9248,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2855277925302709</v>
+        <v>0.287427792530271</v>
       </c>
       <c r="C96">
-        <v>-14.70069000404731</v>
+        <v>-15.04945298045326</v>
       </c>
       <c r="D96">
-        <v>6.982149995952687</v>
+        <v>6.92724701954674</v>
       </c>
       <c r="E96">
-        <v>27.03684</v>
+        <v>27.3307</v>
       </c>
       <c r="F96">
-        <v>27.62284</v>
+        <v>27.9167</v>
       </c>
       <c r="G96">
         <v>5.94</v>
@@ -9284,37 +9284,37 @@
         <v>1.4</v>
       </c>
       <c r="M96">
-        <v>6.513465672000001</v>
+        <v>6.582757860000001</v>
       </c>
       <c r="N96">
-        <v>-5.113465672</v>
+        <v>-5.182757860000001</v>
       </c>
       <c r="O96">
-        <v>-0.8692891642400001</v>
+        <v>-0.8810688362000002</v>
       </c>
       <c r="P96">
-        <v>-4.24417650776</v>
+        <v>-4.301689023800001</v>
       </c>
       <c r="Q96">
-        <v>-3.48417650776</v>
+        <v>-3.541689023800001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.199581455622033</v>
+        <v>1.43033774674644</v>
       </c>
       <c r="T96">
-        <v>26.64622299358044</v>
+        <v>31.97546759229654</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.03653968746977684</v>
+        <v>0.03615505918062129</v>
       </c>
       <c r="W96">
-        <v>0.2271839416946266</v>
+        <v>0.2272746370452095</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.2149393380575109</v>
+        <v>0.212676818709537</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9330,22 +9330,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.287427792530271</v>
+        <v>0.2893277925302709</v>
       </c>
       <c r="C97">
-        <v>-15.04945298045326</v>
+        <v>-15.3973592525456</v>
       </c>
       <c r="D97">
-        <v>6.92724701954674</v>
+        <v>6.873200747454398</v>
       </c>
       <c r="E97">
-        <v>27.3307</v>
+        <v>27.62456</v>
       </c>
       <c r="F97">
-        <v>27.9167</v>
+        <v>28.21056</v>
       </c>
       <c r="G97">
         <v>5.94</v>
@@ -9366,37 +9366,37 @@
         <v>1.4</v>
       </c>
       <c r="M97">
-        <v>6.582757860000001</v>
+        <v>6.652050048</v>
       </c>
       <c r="N97">
-        <v>-5.182757860000001</v>
+        <v>-5.252050048000001</v>
       </c>
       <c r="O97">
-        <v>-0.8810688362000002</v>
+        <v>-0.8928485081600003</v>
       </c>
       <c r="P97">
-        <v>-4.301689023800001</v>
+        <v>-4.359201539840001</v>
       </c>
       <c r="Q97">
-        <v>-3.541689023800001</v>
+        <v>-3.599201539840001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.43033774674644</v>
+        <v>1.776472183433051</v>
       </c>
       <c r="T97">
-        <v>31.97546759229654</v>
+        <v>39.96933449037069</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.03615505918062129</v>
+        <v>0.03577844398082315</v>
       </c>
       <c r="W97">
-        <v>0.2272746370452095</v>
+        <v>0.2273634429093219</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.212676818709537</v>
+        <v>0.2104614351813126</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9412,22 +9412,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2893277925302709</v>
+        <v>0.2912277925302709</v>
       </c>
       <c r="C98">
-        <v>-15.3973592525456</v>
+        <v>-15.74442871707091</v>
       </c>
       <c r="D98">
-        <v>6.873200747454398</v>
+        <v>6.819991282929093</v>
       </c>
       <c r="E98">
-        <v>27.62456</v>
+        <v>27.91842</v>
       </c>
       <c r="F98">
-        <v>28.21056</v>
+        <v>28.50442</v>
       </c>
       <c r="G98">
         <v>5.94</v>
@@ -9448,37 +9448,37 @@
         <v>1.4</v>
       </c>
       <c r="M98">
-        <v>6.652050048</v>
+        <v>6.721342236</v>
       </c>
       <c r="N98">
-        <v>-5.252050047999999</v>
+        <v>-5.321342236</v>
       </c>
       <c r="O98">
-        <v>-0.8928485081599999</v>
+        <v>-0.90462818012</v>
       </c>
       <c r="P98">
-        <v>-4.359201539839999</v>
+        <v>-4.41671405588</v>
       </c>
       <c r="Q98">
-        <v>-3.599201539839999</v>
+        <v>-3.65671405588</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.776472183433046</v>
+        <v>2.353362911244062</v>
       </c>
       <c r="T98">
-        <v>39.96933449037058</v>
+        <v>53.29244598716079</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.03577844398082316</v>
+        <v>0.03540959404287653</v>
       </c>
       <c r="W98">
-        <v>0.2273634429093219</v>
+        <v>0.2274504177246897</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2104614351813128</v>
+        <v>0.2082917296639796</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9494,22 +9494,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2912277925302709</v>
+        <v>0.2931277925302709</v>
       </c>
       <c r="C99">
-        <v>-15.74442871707091</v>
+        <v>-16.09068065937953</v>
       </c>
       <c r="D99">
-        <v>6.819991282929093</v>
+        <v>6.76759934062047</v>
       </c>
       <c r="E99">
-        <v>27.91842</v>
+        <v>28.21228</v>
       </c>
       <c r="F99">
-        <v>28.50442</v>
+        <v>28.79828</v>
       </c>
       <c r="G99">
         <v>5.94</v>
@@ -9530,37 +9530,37 @@
         <v>1.4</v>
       </c>
       <c r="M99">
-        <v>6.721342236</v>
+        <v>6.790634424</v>
       </c>
       <c r="N99">
-        <v>-5.321342236</v>
+        <v>-5.390634424</v>
       </c>
       <c r="O99">
-        <v>-0.90462818012</v>
+        <v>-0.9164078520800001</v>
       </c>
       <c r="P99">
-        <v>-4.41671405588</v>
+        <v>-4.47422657192</v>
       </c>
       <c r="Q99">
-        <v>-3.65671405588</v>
+        <v>-3.71422657192</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.353362911244062</v>
+        <v>3.507144366866092</v>
       </c>
       <c r="T99">
-        <v>53.29244598716079</v>
+        <v>79.93866898074117</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.03540959404287653</v>
+        <v>0.03504827165468391</v>
       </c>
       <c r="W99">
-        <v>0.2274504177246897</v>
+        <v>0.2275356175438255</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2082917296639796</v>
+        <v>0.2061663038510819</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9576,22 +9576,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2931277925302709</v>
+        <v>0.2950277925302709</v>
       </c>
       <c r="C100">
-        <v>-16.09068065937953</v>
+        <v>-16.43613377673067</v>
       </c>
       <c r="D100">
-        <v>6.76759934062047</v>
+        <v>6.716006223269333</v>
       </c>
       <c r="E100">
-        <v>28.21228</v>
+        <v>28.50614</v>
       </c>
       <c r="F100">
-        <v>28.79828</v>
+        <v>29.09214</v>
       </c>
       <c r="G100">
         <v>5.94</v>
@@ -9612,37 +9612,37 @@
         <v>1.4</v>
       </c>
       <c r="M100">
-        <v>6.790634424</v>
+        <v>6.859926612000001</v>
       </c>
       <c r="N100">
-        <v>-5.390634424</v>
+        <v>-5.459926612</v>
       </c>
       <c r="O100">
-        <v>-0.9164078520800001</v>
+        <v>-0.9281875240400002</v>
       </c>
       <c r="P100">
-        <v>-4.47422657192</v>
+        <v>-4.53173908796</v>
       </c>
       <c r="Q100">
-        <v>-3.71422657192</v>
+        <v>-3.77173908796</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.507144366866092</v>
+        <v>6.968488733732184</v>
       </c>
       <c r="T100">
-        <v>79.93866898074117</v>
+        <v>159.8773379614823</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.03504827165468391</v>
+        <v>0.034694248708677</v>
       </c>
       <c r="W100">
-        <v>0.2275356175438255</v>
+        <v>0.227619096154494</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9650,91 +9650,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2061663038510819</v>
+        <v>0.2040838159333942</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2950277925302709</v>
-      </c>
-      <c r="C101">
-        <v>-16.43613377673067</v>
-      </c>
-      <c r="D101">
-        <v>6.716006223269333</v>
-      </c>
-      <c r="E101">
-        <v>28.50614</v>
-      </c>
-      <c r="F101">
-        <v>29.09214</v>
-      </c>
-      <c r="G101">
-        <v>5.94</v>
-      </c>
-      <c r="H101">
-        <v>28.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.16</v>
-      </c>
-      <c r="K101">
-        <v>0.7600000000000002</v>
-      </c>
-      <c r="L101">
-        <v>1.4</v>
-      </c>
-      <c r="M101">
-        <v>6.859926612000001</v>
-      </c>
-      <c r="N101">
-        <v>-5.459926612</v>
-      </c>
-      <c r="O101">
-        <v>-0.9281875240400002</v>
-      </c>
-      <c r="P101">
-        <v>-4.53173908796</v>
-      </c>
-      <c r="Q101">
-        <v>-3.77173908796</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.968488733732184</v>
-      </c>
-      <c r="T101">
-        <v>159.8773379614823</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.034694248708677</v>
-      </c>
-      <c r="W101">
-        <v>0.227619096154494</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2040838159333942</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
